--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -1028,8 +1028,7 @@
     <t>What medication was supplied　医薬品</t>
   </si>
   <si>
-    <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.  
-投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="630">
   <si>
     <t>Property</t>
   </si>
@@ -435,31 +435,52 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
     <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
@@ -470,6 +491,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -498,9 +522,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -516,22 +537,22 @@
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.id</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>処方箋に対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -553,26 +574,25 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.extension</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.use</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.use</t>
@@ -605,7 +625,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.type</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -642,16 +662,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.system</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -660,7 +680,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -672,19 +692,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.value</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -696,7 +716,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.period</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -721,7 +741,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.assigner</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.assigner</t>
@@ -747,63 +767,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>処方箋に対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.11</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier</t>
@@ -1494,12 +1457,6 @@
     <t>MedicationRequest.dispenseRequest.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.extension:instructionForDispense</t>
   </si>
   <si>
@@ -1514,10 +1471,6 @@
   </si>
   <si>
     <t>薬剤単位の調剤指示を格納する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension:expectedRepeatCount</t>
@@ -2345,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO102"/>
+  <dimension ref="A1:AO94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3339,7 +3292,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3358,17 +3311,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3405,16 +3356,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -3438,7 +3387,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -3452,43 +3401,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3536,7 +3483,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3545,7 +3492,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3557,7 +3504,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -3575,11 +3522,11 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>81</v>
@@ -3588,13 +3535,13 @@
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>150</v>
@@ -3605,7 +3552,9 @@
       <c r="N11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="O11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3641,17 +3590,19 @@
         <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3663,43 +3614,41 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3711,16 +3660,16 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3758,19 +3707,17 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3785,29 +3732,31 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3828,7 +3777,7 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>168</v>
@@ -3836,7 +3785,9 @@
       <c r="M13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3885,53 +3836,53 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3943,17 +3894,15 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3990,40 +3939,40 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF14" t="s" s="2">
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -4041,26 +3990,26 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>180</v>
@@ -4069,11 +4018,9 @@
         <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4097,43 +4044,43 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4142,21 +4089,21 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4173,25 +4120,25 @@
         <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4216,13 +4163,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4240,7 +4187,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4261,21 +4208,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4283,7 +4230,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4298,26 +4245,26 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4335,13 +4282,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4359,7 +4306,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4380,21 +4327,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4417,24 +4364,26 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>82</v>
@@ -4476,7 +4425,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4497,21 +4446,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4519,7 +4468,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4534,15 +4483,17 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4591,7 +4542,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4612,21 +4563,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4649,17 +4600,15 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4708,7 +4657,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4729,25 +4678,23 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4765,19 +4712,19 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4827,13 +4774,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4842,29 +4789,31 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>159</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4873,7 +4822,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4885,15 +4834,17 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4942,53 +4893,53 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -5000,17 +4951,15 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5047,40 +4996,40 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AD23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF23" t="s" s="2">
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5091,33 +5040,33 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>180</v>
@@ -5126,11 +5075,9 @@
         <v>181</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5154,43 +5101,43 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5199,21 +5146,21 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5230,25 +5177,25 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5273,13 +5220,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5297,7 +5244,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5318,21 +5265,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5340,7 +5287,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -5355,26 +5302,26 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>199</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5392,13 +5339,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5416,7 +5363,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5437,21 +5384,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5474,24 +5421,26 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>82</v>
@@ -5533,7 +5482,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5554,21 +5503,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5576,7 +5525,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5591,15 +5540,17 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5648,7 +5599,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5669,21 +5620,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5706,17 +5657,15 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5765,7 +5714,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5786,25 +5735,23 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5813,7 +5760,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5822,19 +5769,19 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5884,13 +5831,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5899,27 +5846,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>159</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>166</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5927,7 +5874,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -5936,21 +5883,23 @@
         <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5975,13 +5924,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5999,10 +5948,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>91</v>
@@ -6011,19 +5960,19 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6031,21 +5980,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6057,16 +6006,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>140</v>
+        <v>267</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6092,52 +6041,52 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>171</v>
+        <v>272</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6148,10 +6097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6159,7 +6108,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -6177,17 +6126,15 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6211,13 +6158,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>185</v>
+        <v>277</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>186</v>
+        <v>278</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6235,10 +6182,10 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>91</v>
@@ -6250,27 +6197,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>188</v>
+        <v>280</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6281,7 +6228,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6290,23 +6237,21 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>192</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
+        <v>284</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6330,13 +6275,11 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6354,13 +6297,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6372,24 +6315,24 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6397,7 +6340,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>91</v>
@@ -6412,26 +6355,24 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6449,13 +6390,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6473,7 +6414,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>208</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6488,27 +6429,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>212</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6516,7 +6457,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6525,22 +6466,22 @@
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>299</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>301</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6590,7 +6531,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6611,21 +6552,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>217</v>
+        <v>303</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6648,13 +6589,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>305</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6705,7 +6646,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>224</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6726,21 +6667,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>225</v>
+        <v>308</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6748,7 +6689,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>91</v>
@@ -6763,16 +6704,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>310</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>232</v>
+        <v>313</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6822,10 +6763,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>91</v>
@@ -6837,27 +6778,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>234</v>
+        <v>316</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>235</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6874,22 +6815,22 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6915,13 +6856,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6939,7 +6880,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6954,27 +6895,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6997,16 +6938,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>330</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7032,13 +6973,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7056,7 +6997,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7071,27 +7012,27 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>334</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>335</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7099,31 +7040,31 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7149,13 +7090,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7173,13 +7114,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -7188,16 +7129,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7205,10 +7146,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7216,10 +7157,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7228,20 +7169,18 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>346</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7266,11 +7205,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7288,13 +7229,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7303,27 +7244,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>301</v>
+        <v>351</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7346,16 +7287,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>111</v>
+        <v>355</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7381,13 +7322,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7405,7 +7346,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7420,16 +7361,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>308</v>
+        <v>358</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>359</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7437,10 +7378,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7457,22 +7398,22 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7522,7 +7463,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7537,16 +7478,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7554,10 +7495,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7580,15 +7521,17 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>318</v>
+        <v>197</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7613,13 +7556,11 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7637,7 +7578,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7652,13 +7593,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7669,10 +7610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7680,7 +7621,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7692,19 +7633,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>377</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7754,10 +7695,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7769,27 +7710,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>330</v>
+        <v>379</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7797,10 +7738,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7809,19 +7750,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>333</v>
+        <v>197</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>336</v>
+        <v>383</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7847,13 +7788,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7871,13 +7812,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7886,27 +7827,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>337</v>
+        <v>386</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>339</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>340</v>
+        <v>389</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>341</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7917,7 +7858,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7929,16 +7870,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>392</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>394</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>346</v>
+        <v>395</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7988,13 +7929,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8003,27 +7944,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>347</v>
+        <v>396</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8043,19 +7984,19 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>355</v>
+        <v>402</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8105,7 +8046,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8120,16 +8061,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>356</v>
+        <v>403</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>404</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8078,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8148,10 +8089,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8163,15 +8104,17 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8220,13 +8163,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8235,27 +8178,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8266,7 +8209,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8278,16 +8221,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8337,13 +8280,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8352,16 +8295,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8369,10 +8312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8392,21 +8335,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>156</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8454,7 +8397,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8469,16 +8412,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8486,10 +8429,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8509,19 +8452,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
+        <v>422</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8547,11 +8490,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8569,7 +8514,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8584,13 +8529,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8601,10 +8546,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8615,7 +8560,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8627,16 +8572,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>428</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8686,13 +8631,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>427</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8701,16 +8646,16 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>432</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8718,10 +8663,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,16 +8689,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>434</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8779,13 +8724,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8803,7 +8748,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8818,27 +8763,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,16 +8806,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8920,7 +8865,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8935,16 +8880,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8952,10 +8897,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8966,7 +8911,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8975,20 +8920,18 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9037,13 +8980,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9052,13 +8995,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9069,10 +9012,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9083,7 +9026,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9092,20 +9035,18 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9154,19 +9095,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>176</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9175,7 +9116,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>177</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9186,10 +9127,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9209,20 +9150,18 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>422</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>423</v>
+        <v>137</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9259,19 +9198,17 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>183</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9283,16 +9220,16 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9303,12 +9240,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9317,7 +9256,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9326,21 +9265,19 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>149</v>
+        <v>458</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>430</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9388,28 +9325,28 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>183</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9420,12 +9357,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9446,17 +9385,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9481,13 +9418,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9505,19 +9442,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>183</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9463,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9537,14 +9474,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9557,24 +9494,26 @@
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9622,7 +9561,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9634,16 +9573,16 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>134</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9654,10 +9593,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9668,7 +9607,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9683,13 +9622,13 @@
         <v>447</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9739,13 +9678,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9754,13 +9693,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>453</v>
+        <v>475</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9771,10 +9710,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9785,7 +9724,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9797,17 +9736,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>174</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9856,19 +9793,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>176</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9877,7 +9814,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>177</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9888,21 +9825,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9914,15 +9851,17 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>460</v>
+        <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>180</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9971,28 +9910,28 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>183</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>464</v>
+        <v>177</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10003,42 +9942,46 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10086,19 +10029,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10107,7 +10050,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10118,10 +10061,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10132,7 +10075,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10144,15 +10087,17 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>137</v>
+        <v>480</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10189,29 +10134,31 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>177</v>
+        <v>479</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>484</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10220,25 +10167,23 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10247,7 +10192,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10259,15 +10204,17 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10316,19 +10263,19 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>177</v>
+        <v>487</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10337,7 +10284,7 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10348,14 +10295,12 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10376,15 +10321,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10433,19 +10380,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>177</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10454,7 +10401,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10465,45 +10412,45 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>140</v>
+        <v>498</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>146</v>
+        <v>499</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10552,28 +10499,28 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>134</v>
+        <v>501</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10584,10 +10531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10610,17 +10557,15 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>488</v>
+        <v>174</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10669,7 +10614,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>176</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10681,7 +10626,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10690,7 +10635,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>491</v>
+        <v>177</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10701,21 +10646,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10727,15 +10672,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10772,31 +10719,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10805,7 +10752,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10816,21 +10763,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10839,19 +10786,19 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>137</v>
+        <v>346</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>138</v>
+        <v>505</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>174</v>
+        <v>506</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>140</v>
+        <v>507</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10901,19 +10848,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>177</v>
+        <v>508</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10922,61 +10869,61 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>171</v>
+        <v>510</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>137</v>
+        <v>346</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>514</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11020,19 +10967,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11041,21 +10988,21 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>134</v>
+        <v>518</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11078,16 +11025,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11137,7 +11084,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11146,33 +11093,33 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>502</v>
+        <v>527</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11195,16 +11142,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11254,7 +11201,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11263,10 +11210,10 @@
         <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>484</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11275,21 +11222,21 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11312,16 +11259,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>509</v>
+        <v>532</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>534</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11371,7 +11318,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11389,10 +11336,10 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11429,20 +11376,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>174</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11490,7 +11433,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>176</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11502,16 +11445,16 @@
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>517</v>
+        <v>177</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11522,21 +11465,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11548,15 +11491,17 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11593,31 +11538,31 @@
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11626,7 +11571,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11637,21 +11582,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11660,21 +11605,23 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>540</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>138</v>
+        <v>541</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>174</v>
+        <v>542</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11710,31 +11657,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>177</v>
+        <v>545</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11743,21 +11690,21 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>171</v>
+        <v>546</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11774,28 +11721,30 @@
         <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>359</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="R81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11815,13 +11764,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11839,7 +11788,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11848,7 +11797,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11860,21 +11809,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>527</v>
+        <v>557</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11897,26 +11846,24 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>359</v>
+        <v>173</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" t="s" s="2">
-        <v>532</v>
-      </c>
+      <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>82</v>
@@ -11958,7 +11905,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11967,7 +11914,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11979,21 +11926,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>535</v>
+        <v>565</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12013,27 +11960,27 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>537</v>
+        <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>538</v>
+        <v>567</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>82</v>
@@ -12075,7 +12022,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>536</v>
+        <v>571</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12084,7 +12031,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -12093,24 +12040,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>542</v>
+        <v>573</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>543</v>
+        <v>565</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12130,27 +12077,29 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>111</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>82</v>
@@ -12192,7 +12141,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>544</v>
+        <v>580</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12201,10 +12150,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12213,21 +12162,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>501</v>
+        <v>581</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>502</v>
+        <v>565</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12250,16 +12199,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>504</v>
+        <v>583</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>584</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>550</v>
+        <v>342</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12309,7 +12258,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>582</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12327,13 +12276,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>552</v>
+        <v>586</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12341,10 +12290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>553</v>
+        <v>587</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>553</v>
+        <v>587</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12367,13 +12316,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>167</v>
+        <v>447</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>168</v>
+        <v>588</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>169</v>
+        <v>589</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12424,7 +12373,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>170</v>
+        <v>587</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12436,16 +12385,16 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>171</v>
+        <v>591</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12456,21 +12405,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12482,17 +12431,15 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12529,40 +12476,40 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF87" t="s" s="2">
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12573,21 +12520,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12596,23 +12543,21 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>556</v>
+        <v>136</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>180</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>181</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12660,19 +12605,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>183</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12681,32 +12626,32 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>562</v>
+        <v>177</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12718,24 +12663,24 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>468</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>567</v>
+        <v>153</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q89" t="s" s="2">
-        <v>568</v>
-      </c>
+      <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12755,13 +12700,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>569</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12779,19 +12724,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>470</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12800,21 +12745,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>572</v>
+        <v>134</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12822,7 +12767,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>91</v>
@@ -12834,27 +12779,27 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12872,13 +12817,11 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -12896,10 +12839,10 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>91</v>
@@ -12914,24 +12857,24 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>581</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12951,27 +12894,27 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -12989,13 +12932,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13013,7 +12956,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13022,7 +12965,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13031,24 +12974,24 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>581</v>
+        <v>609</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13068,29 +13011,27 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>611</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13132,7 +13073,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13147,38 +13088,38 @@
         <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>581</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13190,16 +13131,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>599</v>
+        <v>618</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>355</v>
+        <v>621</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13249,13 +13190,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13270,10 +13211,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13281,10 +13222,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13295,7 +13236,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13307,15 +13248,17 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>460</v>
+        <v>624</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13364,13 +13307,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13379,952 +13322,18 @@
         <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y98" s="2"/>
-      <c r="Z98" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -435,21 +435,21 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -459,28 +459,7 @@
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>MedicationRequest.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>MedicationRequest.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
@@ -491,9 +470,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -522,6 +498,9 @@
 </t>
   </si>
   <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -537,22 +516,22 @@
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>処方箋に対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
+    <t>MedicationRequest.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -574,25 +553,26 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
+    <t>MedicationRequest.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
+    <t>MedicationRequest.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.use</t>
@@ -625,7 +605,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
+    <t>MedicationRequest.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -662,16 +642,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+    <t>MedicationRequest.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -680,7 +660,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.11</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -692,19 +672,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
+    <t>MedicationRequest.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -716,7 +696,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
+    <t>MedicationRequest.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -741,7 +721,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
+    <t>MedicationRequest.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.assigner</t>
@@ -767,6 +747,63 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>処方箋に対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier</t>
@@ -1457,6 +1494,12 @@
     <t>MedicationRequest.dispenseRequest.extension</t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest.extension:instructionForDispense</t>
   </si>
   <si>
@@ -1471,6 +1514,10 @@
   </si>
   <si>
     <t>薬剤単位の調剤指示を格納する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension:expectedRepeatCount</t>
@@ -2298,7 +2345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3292,7 +3339,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3311,15 +3358,17 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3356,14 +3405,16 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -3387,7 +3438,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -3401,41 +3452,43 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3483,7 +3536,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3492,7 +3545,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3504,7 +3557,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -3522,11 +3575,11 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>81</v>
@@ -3535,13 +3588,13 @@
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>150</v>
@@ -3552,9 +3605,7 @@
       <c r="N11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3590,19 +3641,17 @@
         <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3614,41 +3663,43 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3660,16 +3711,16 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3707,17 +3758,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AC12" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3732,31 +3785,29 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3777,7 +3828,7 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>168</v>
@@ -3785,9 +3836,7 @@
       <c r="M13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3836,53 +3885,53 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3894,15 +3943,17 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" s="2"/>
+      <c r="N14" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3939,31 +3990,31 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -3972,7 +4023,7 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -3990,26 +4041,26 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>180</v>
@@ -4018,9 +4069,11 @@
         <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4044,43 +4097,43 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4089,21 +4142,21 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4120,25 +4173,25 @@
         <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4163,13 +4216,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4187,7 +4240,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4208,21 +4261,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>134</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4230,7 +4283,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4245,26 +4298,26 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4282,13 +4335,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4306,7 +4359,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4327,21 +4380,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4364,26 +4417,24 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>82</v>
@@ -4425,7 +4476,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4446,21 +4497,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4468,7 +4519,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4483,17 +4534,15 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4542,7 +4591,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4563,21 +4612,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4600,15 +4649,17 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4657,7 +4708,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4678,23 +4729,25 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4712,19 +4765,19 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4774,13 +4827,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4789,31 +4842,29 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>241</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4822,7 +4873,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4834,17 +4885,15 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>244</v>
+        <v>168</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4893,53 +4942,53 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4951,15 +5000,17 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4996,31 +5047,31 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5029,7 +5080,7 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5040,33 +5091,33 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>180</v>
@@ -5075,9 +5126,11 @@
         <v>181</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5101,43 +5154,43 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5146,21 +5199,21 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5177,25 +5230,25 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5220,13 +5273,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5244,7 +5297,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5265,21 +5318,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>134</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5287,7 +5340,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -5302,26 +5355,26 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5339,13 +5392,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5363,7 +5416,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5384,21 +5437,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5421,26 +5474,24 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>82</v>
@@ -5482,7 +5533,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5503,21 +5554,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5525,7 +5576,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5540,17 +5591,15 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5599,7 +5648,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5620,21 +5669,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5657,15 +5706,17 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5714,7 +5765,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5735,23 +5786,25 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5760,7 +5813,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5769,19 +5822,19 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5831,13 +5884,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5846,27 +5899,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>241</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5874,7 +5927,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
@@ -5883,23 +5936,21 @@
         <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5924,13 +5975,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5948,10 +5999,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>91</v>
@@ -5960,19 +6011,19 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5980,21 +6031,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6006,16 +6057,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6041,52 +6092,52 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>177</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6097,10 +6148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6108,7 +6159,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -6126,15 +6177,17 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>180</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6158,13 +6211,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>277</v>
+        <v>185</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6182,10 +6235,10 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>187</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>91</v>
@@ -6197,27 +6250,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6228,7 +6281,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6237,21 +6290,23 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6275,11 +6330,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>286</v>
+        <v>198</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6297,13 +6354,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6315,24 +6372,24 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>188</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6340,7 +6397,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>91</v>
@@ -6355,24 +6412,26 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6390,13 +6449,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6414,7 +6473,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6429,27 +6488,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>212</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6457,7 +6516,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6466,22 +6525,22 @@
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>299</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>302</v>
+        <v>252</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6531,7 +6590,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>216</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6552,21 +6611,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>220</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6589,13 +6648,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>305</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>222</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>223</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6646,7 +6705,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>304</v>
+        <v>224</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6667,21 +6726,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>308</v>
+        <v>225</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6689,7 +6748,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>91</v>
@@ -6704,16 +6763,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>230</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>231</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>313</v>
+        <v>232</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6763,10 +6822,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>91</v>
@@ -6778,27 +6837,27 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>234</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>318</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6815,22 +6874,22 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>320</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6856,13 +6915,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6880,7 +6939,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6895,27 +6954,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6938,16 +6997,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>333</v>
+        <v>280</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6973,13 +7032,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6997,7 +7056,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7012,27 +7071,27 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7040,31 +7099,31 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>339</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>288</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7090,13 +7149,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7114,13 +7173,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -7129,16 +7188,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>336</v>
+        <v>294</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7146,10 +7205,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7157,10 +7216,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7169,18 +7228,20 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>346</v>
+        <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7205,13 +7266,11 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7229,13 +7288,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7244,27 +7303,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>352</v>
+        <v>294</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7287,16 +7346,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>356</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>357</v>
+        <v>304</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>342</v>
+        <v>305</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7322,13 +7381,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7346,7 +7405,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7361,16 +7420,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7378,10 +7437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7398,22 +7457,22 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7463,7 +7522,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7478,16 +7537,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7495,10 +7554,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7521,17 +7580,15 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>197</v>
+        <v>318</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7556,11 +7613,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7578,7 +7637,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7593,13 +7652,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>373</v>
+        <v>321</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7610,10 +7669,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7621,7 +7680,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7633,19 +7692,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7695,10 +7754,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7710,27 +7769,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7738,10 +7797,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7750,19 +7809,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>383</v>
+        <v>336</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7788,13 +7847,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7812,13 +7871,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7827,27 +7886,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>386</v>
+        <v>337</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7858,7 +7917,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7870,16 +7929,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>395</v>
+        <v>346</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7929,13 +7988,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7944,27 +8003,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7984,19 +8043,19 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>402</v>
+        <v>355</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8046,7 +8105,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8061,16 +8120,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>404</v>
+        <v>357</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8078,10 +8137,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8089,10 +8148,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8104,17 +8163,15 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>105</v>
+        <v>359</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8163,13 +8220,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8178,27 +8235,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8209,7 +8266,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8221,16 +8278,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>409</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8280,13 +8337,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8295,16 +8352,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>413</v>
+        <v>339</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8312,10 +8369,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8335,21 +8392,21 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>156</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8397,7 +8454,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8412,16 +8469,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8429,10 +8486,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8452,19 +8509,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>423</v>
+        <v>383</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8490,13 +8547,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8514,7 +8569,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8529,13 +8584,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8546,10 +8601,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8560,7 +8615,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8572,16 +8627,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8631,13 +8686,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8646,16 +8701,16 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8663,10 +8718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8689,16 +8744,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8724,13 +8779,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8748,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8763,27 +8818,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>438</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>401</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8806,16 +8861,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8865,7 +8920,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8880,16 +8935,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8897,10 +8952,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8911,7 +8966,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8920,18 +8975,20 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8980,13 +9037,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -8995,13 +9052,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>451</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9012,10 +9069,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9026,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9035,18 +9092,20 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>419</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9095,19 +9154,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>176</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9116,7 +9175,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>177</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9127,10 +9186,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9150,18 +9209,20 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>136</v>
+        <v>422</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9198,17 +9259,19 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>183</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9220,16 +9283,16 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9240,14 +9303,12 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9256,7 +9317,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9265,19 +9326,21 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>458</v>
+        <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9325,28 +9388,28 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>183</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9357,14 +9420,12 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9385,15 +9446,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9418,13 +9481,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9442,19 +9505,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>183</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9463,7 +9526,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9474,14 +9537,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9494,26 +9557,24 @@
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>441</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9561,7 +9622,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9573,16 +9634,16 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>134</v>
+        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9593,10 +9654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9607,7 +9668,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9622,13 +9683,13 @@
         <v>447</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9678,13 +9739,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9693,13 +9754,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9710,10 +9771,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9724,7 +9785,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9736,15 +9797,17 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>455</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>174</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9793,19 +9856,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>176</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9814,7 +9877,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>177</v>
+        <v>458</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9825,21 +9888,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9851,17 +9914,15 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>136</v>
+        <v>460</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>180</v>
+        <v>461</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9910,28 +9971,28 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>183</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>177</v>
+        <v>464</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -9942,46 +10003,42 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10029,19 +10086,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -10050,7 +10107,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10061,10 +10118,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10075,7 +10132,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10087,17 +10144,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>480</v>
+        <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10134,31 +10189,29 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>479</v>
+        <v>177</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>484</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10167,23 +10220,25 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10192,7 +10247,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10204,17 +10259,15 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10263,19 +10316,19 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>487</v>
+        <v>177</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10284,7 +10337,7 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10295,12 +10348,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10321,17 +10376,15 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10380,19 +10433,19 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>492</v>
+        <v>177</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10401,7 +10454,7 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10412,45 +10465,45 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>498</v>
+        <v>140</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>499</v>
+        <v>146</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10499,28 +10552,28 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>501</v>
+        <v>134</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10531,10 +10584,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10557,15 +10610,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>173</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>174</v>
+        <v>488</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10614,7 +10669,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>176</v>
+        <v>487</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10626,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10635,7 +10690,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>177</v>
+        <v>491</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10646,21 +10701,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10672,17 +10727,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10719,31 +10772,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10752,7 +10805,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10763,21 +10816,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10786,19 +10839,19 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>505</v>
+        <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>506</v>
+        <v>174</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>507</v>
+        <v>140</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10848,19 +10901,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>508</v>
+        <v>177</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10869,61 +10922,61 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>510</v>
+        <v>171</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q74" t="s" s="2">
-        <v>516</v>
-      </c>
+      <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
         <v>82</v>
       </c>
@@ -10967,19 +11020,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -10988,21 +11041,21 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>518</v>
+        <v>134</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11025,16 +11078,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>522</v>
+        <v>497</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11084,7 +11137,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11093,33 +11146,33 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>500</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>527</v>
+        <v>502</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11142,16 +11195,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11201,7 +11254,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11210,10 +11263,10 @@
         <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>484</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11222,21 +11275,21 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11259,16 +11312,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>534</v>
+        <v>499</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11318,7 +11371,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11336,10 +11389,10 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11350,10 +11403,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11376,16 +11429,20 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>174</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11433,7 +11490,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>176</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11445,16 +11502,16 @@
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>177</v>
+        <v>517</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11465,21 +11522,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11491,17 +11548,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11538,31 +11593,31 @@
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11571,7 +11626,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11582,21 +11637,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11605,23 +11660,21 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>540</v>
+        <v>137</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>541</v>
+        <v>138</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>542</v>
+        <v>174</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11657,31 +11710,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>545</v>
+        <v>177</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11690,21 +11743,21 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>546</v>
+        <v>171</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11721,30 +11774,28 @@
         <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>111</v>
+        <v>359</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q81" t="s" s="2">
-        <v>552</v>
-      </c>
+      <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11764,13 +11815,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11788,7 +11839,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11797,7 +11848,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11809,21 +11860,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>557</v>
+        <v>527</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11846,24 +11897,26 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="R82" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>82</v>
@@ -11905,7 +11958,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>563</v>
+        <v>533</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11914,7 +11967,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11926,21 +11979,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>565</v>
+        <v>535</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11960,27 +12013,27 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>105</v>
+        <v>537</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>82</v>
@@ -12022,7 +12075,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>571</v>
+        <v>536</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12031,7 +12084,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -12040,24 +12093,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>565</v>
+        <v>543</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12077,29 +12130,27 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>496</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>575</v>
+        <v>545</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>576</v>
+        <v>546</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>82</v>
@@ -12141,7 +12192,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>580</v>
+        <v>544</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12150,10 +12201,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>500</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12162,21 +12213,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>581</v>
+        <v>501</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>565</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12199,16 +12250,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>583</v>
+        <v>504</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>584</v>
+        <v>548</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>585</v>
+        <v>549</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>342</v>
+        <v>550</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12258,7 +12309,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12276,13 +12327,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>586</v>
+        <v>552</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12290,10 +12341,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12316,13 +12367,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>447</v>
+        <v>167</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>588</v>
+        <v>168</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>589</v>
+        <v>169</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12373,7 +12424,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>587</v>
+        <v>170</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12385,16 +12436,16 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>591</v>
+        <v>171</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12405,21 +12456,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12431,15 +12482,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M87" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N87" s="2"/>
+      <c r="N87" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12476,31 +12529,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12509,7 +12562,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12520,21 +12573,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>593</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>593</v>
+        <v>555</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12543,21 +12596,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>136</v>
+        <v>556</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>180</v>
+        <v>557</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>181</v>
+        <v>558</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12605,19 +12660,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>183</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12626,32 +12681,32 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>177</v>
+        <v>562</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12663,24 +12718,24 @@
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>468</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>153</v>
+        <v>567</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12700,13 +12755,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12724,19 +12779,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>470</v>
+        <v>571</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12745,21 +12800,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>134</v>
+        <v>572</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12767,7 +12822,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>91</v>
@@ -12779,27 +12834,27 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12817,11 +12872,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -12839,10 +12896,10 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>91</v>
@@ -12857,24 +12914,24 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>600</v>
+        <v>581</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12894,27 +12951,27 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>585</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -12932,13 +12989,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -12956,7 +13013,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12965,7 +13022,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -12974,24 +13031,24 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>608</v>
+        <v>589</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>609</v>
+        <v>581</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13011,27 +13068,29 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>611</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13073,7 +13132,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13088,38 +13147,38 @@
         <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13131,16 +13190,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>621</v>
+        <v>355</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13190,13 +13249,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13211,10 +13270,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13222,10 +13281,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13236,7 +13295,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13248,17 +13307,15 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>624</v>
+        <v>460</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13307,13 +13364,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13322,18 +13379,952 @@
         <v>103</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y98" s="2"/>
+      <c r="Z98" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AL94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM94" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AN94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO94" t="s" s="2">
+      <c r="N100" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="645">
   <si>
     <t>Property</t>
   </si>
@@ -651,7 +651,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -660,7 +660,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -831,9 +831,6 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
@@ -6431,7 +6428,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6505,7 +6502,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>212</v>
@@ -6622,7 +6619,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>220</v>
@@ -6737,7 +6734,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>228</v>
@@ -6854,10 +6851,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6883,13 +6880,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6918,11 +6915,11 @@
         <v>184</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6939,7 +6936,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6954,16 +6951,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6971,10 +6968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7000,13 +6997,13 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7032,14 +7029,14 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7056,7 +7053,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7071,13 +7068,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7088,10 +7085,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7117,13 +7114,13 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7152,11 +7149,11 @@
         <v>184</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7173,7 +7170,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7188,16 +7185,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7205,10 +7202,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7234,13 +7231,13 @@
         <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7270,7 +7267,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7288,7 +7285,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7306,13 +7303,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>301</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7320,10 +7317,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7349,13 +7346,13 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7384,11 +7381,11 @@
         <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7405,7 +7402,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7420,16 +7417,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7437,10 +7434,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7463,16 +7460,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7522,7 +7519,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7543,7 +7540,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7554,10 +7551,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7580,13 +7577,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7637,7 +7634,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7658,7 +7655,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7669,10 +7666,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7695,16 +7692,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7754,7 +7751,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7769,27 +7766,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7812,16 +7809,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7871,7 +7868,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7886,27 +7883,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>341</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7929,16 +7926,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7988,7 +7985,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8003,27 +8000,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8046,16 +8043,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8105,7 +8102,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8120,16 +8117,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8134,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8163,13 +8160,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8220,7 +8217,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8235,27 +8232,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8278,16 +8275,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8337,7 +8334,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8352,16 +8349,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8369,10 +8366,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,16 +8392,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8454,7 +8451,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8469,16 +8466,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8486,10 +8483,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8515,13 +8512,13 @@
         <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8547,11 +8544,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8569,7 +8566,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8584,13 +8581,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8601,10 +8598,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8627,16 +8624,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8686,7 +8683,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8707,10 +8704,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8718,10 +8715,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8747,13 +8744,13 @@
         <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8779,14 +8776,14 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8803,7 +8800,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8818,27 +8815,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,16 +8858,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8920,7 +8917,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8935,16 +8932,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AN56" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8952,10 +8949,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8978,16 +8975,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9037,7 +9034,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9052,13 +9049,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9069,10 +9066,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9098,13 +9095,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9154,7 +9151,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9175,7 +9172,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9186,10 +9183,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9212,16 +9209,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9271,7 +9268,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9286,13 +9283,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9303,10 +9300,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9332,14 +9329,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9388,7 +9385,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9403,13 +9400,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9420,10 +9417,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9449,13 +9446,13 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9481,14 +9478,14 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9505,7 +9502,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9526,7 +9523,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9537,10 +9534,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,16 +9560,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9622,7 +9619,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9637,13 +9634,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9654,10 +9651,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9680,16 +9677,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9739,7 +9736,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9754,13 +9751,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9771,10 +9768,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9797,16 +9794,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9856,7 +9853,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9877,7 +9874,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9888,10 +9885,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9914,13 +9911,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9971,7 +9968,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9989,10 +9986,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10003,10 +10000,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10032,10 +10029,10 @@
         <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10118,10 +10115,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10147,10 +10144,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10231,13 +10228,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10259,13 +10256,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10325,7 +10322,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10348,13 +10345,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10376,13 +10373,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10442,7 +10439,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10465,14 +10462,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10494,10 +10491,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10552,7 +10549,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10584,10 +10581,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10610,16 +10607,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10669,7 +10666,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10690,7 +10687,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10701,10 +10698,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10816,10 +10813,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10933,14 +10930,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10962,10 +10959,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11020,7 +11017,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11049,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11078,16 +11075,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11137,7 +11134,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11146,33 +11143,33 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AK75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11195,16 +11192,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11254,7 +11251,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11275,7 +11272,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11286,10 +11283,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11312,16 +11309,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11371,7 +11368,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11392,7 +11389,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11400,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11432,16 +11429,16 @@
         <v>221</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11490,7 +11487,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11508,10 +11505,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11522,10 +11519,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11637,10 +11634,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11754,10 +11751,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11780,16 +11777,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11839,16 +11836,16 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI81" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11860,21 +11857,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11897,69 +11894,69 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>533</v>
-      </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11967,7 +11964,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11979,21 +11976,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12016,16 +12013,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12075,7 +12072,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12093,24 +12090,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>543</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12133,16 +12130,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="N84" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12192,7 +12189,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12201,33 +12198,33 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12250,16 +12247,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12309,7 +12306,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12327,10 +12324,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12341,10 +12338,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12456,10 +12453,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12573,10 +12570,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12599,19 +12596,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12660,7 +12657,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12681,21 +12678,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12721,20 +12718,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q89" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12758,28 +12755,28 @@
         <v>184</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12800,21 +12797,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>573</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12840,63 +12837,63 @@
         <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12917,21 +12914,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>581</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12957,72 +12954,72 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI91" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13034,21 +13031,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13074,65 +13071,65 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13153,21 +13150,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13190,16 +13187,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13249,7 +13246,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13270,10 +13267,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13281,10 +13278,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13307,13 +13304,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13364,7 +13361,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13382,10 +13379,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13396,10 +13393,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13511,10 +13508,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13628,14 +13625,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13657,10 +13654,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13715,7 +13712,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13747,10 +13744,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13776,13 +13773,13 @@
         <v>191</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13812,7 +13809,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13830,7 +13827,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13848,24 +13845,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>616</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13891,13 +13888,13 @@
         <v>191</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13923,14 +13920,14 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z99" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="Z99" t="s" s="2">
-        <v>622</v>
-      </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
       </c>
@@ -13947,7 +13944,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13965,24 +13962,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="AM99" t="s" s="2">
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>625</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14005,16 +14002,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>629</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14064,7 +14061,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14079,13 +14076,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14096,14 +14093,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14122,16 +14119,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14181,7 +14178,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14202,7 +14199,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14213,10 +14210,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14239,16 +14236,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14298,7 +14295,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14313,13 +14310,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -831,6 +831,9 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
@@ -6428,7 +6431,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>212</v>
@@ -6619,7 +6622,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>220</v>
@@ -6734,7 +6737,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>228</v>
@@ -6851,10 +6854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6880,13 +6883,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6915,10 +6918,10 @@
         <v>184</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6936,7 +6939,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6951,16 +6954,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6968,10 +6971,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6997,13 +7000,13 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7029,13 +7032,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7053,7 +7056,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7068,13 +7071,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7085,10 +7088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7114,13 +7117,13 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7149,10 +7152,10 @@
         <v>184</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7170,7 +7173,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7185,16 +7188,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7202,10 +7205,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7231,13 +7234,13 @@
         <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7267,7 +7270,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7285,7 +7288,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7303,13 +7306,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7317,10 +7320,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7346,13 +7349,13 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7381,10 +7384,10 @@
         <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7402,7 +7405,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7417,16 +7420,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7434,10 +7437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7460,16 +7463,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7519,7 +7522,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7540,7 +7543,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7551,10 +7554,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7577,13 +7580,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7634,7 +7637,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7655,7 +7658,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7666,10 +7669,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7692,16 +7695,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7751,7 +7754,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7766,27 +7769,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7809,16 +7812,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7868,7 +7871,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7883,27 +7886,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7926,16 +7929,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7985,7 +7988,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8000,27 +8003,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8043,16 +8046,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8102,7 +8105,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8117,16 +8120,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8134,10 +8137,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8160,13 +8163,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8217,7 +8220,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8232,27 +8235,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8275,16 +8278,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8334,7 +8337,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8349,16 +8352,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8366,10 +8369,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8392,16 +8395,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8451,7 +8454,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8466,16 +8469,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8483,10 +8486,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8512,13 +8515,13 @@
         <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8544,11 +8547,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8566,7 +8569,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8581,13 +8584,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8598,10 +8601,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8624,16 +8627,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8683,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8704,10 +8707,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8715,10 +8718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,13 +8747,13 @@
         <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8776,13 +8779,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8800,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8815,27 +8818,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8858,16 +8861,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8917,7 +8920,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8932,16 +8935,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8949,10 +8952,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8975,16 +8978,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9034,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9049,13 +9052,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9066,10 +9069,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9095,13 +9098,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9151,7 +9154,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9172,7 +9175,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9183,10 +9186,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9209,16 +9212,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9268,7 +9271,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9283,13 +9286,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9300,10 +9303,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9329,14 +9332,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9385,7 +9388,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9400,13 +9403,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9417,10 +9420,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9446,13 +9449,13 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9478,13 +9481,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9502,7 +9505,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9523,7 +9526,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9534,10 +9537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9560,16 +9563,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9619,7 +9622,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9634,13 +9637,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9651,10 +9654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9677,16 +9680,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9736,7 +9739,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9751,13 +9754,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9768,10 +9771,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9794,16 +9797,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9853,7 +9856,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9874,7 +9877,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9885,10 +9888,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9911,13 +9914,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9968,7 +9971,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9986,10 +9989,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10000,10 +10003,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10029,10 +10032,10 @@
         <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10115,10 +10118,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10144,10 +10147,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10228,13 +10231,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10256,13 +10259,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10322,7 +10325,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10345,13 +10348,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10373,13 +10376,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10439,7 +10442,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10462,14 +10465,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10491,10 +10494,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10549,7 +10552,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10581,10 +10584,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10607,16 +10610,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10666,7 +10669,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10687,7 +10690,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10698,10 +10701,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10813,10 +10816,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10930,14 +10933,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10959,10 +10962,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11017,7 +11020,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11049,10 +11052,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11075,16 +11078,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11134,7 +11137,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11143,10 +11146,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11155,21 +11158,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11192,16 +11195,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11251,7 +11254,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11272,7 +11275,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11283,10 +11286,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11309,16 +11312,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11368,7 +11371,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11389,7 +11392,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11400,10 +11403,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11429,16 +11432,16 @@
         <v>221</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11487,7 +11490,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11505,10 +11508,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11519,10 +11522,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11634,10 +11637,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11751,10 +11754,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11777,16 +11780,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11836,7 +11839,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11845,7 +11848,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11857,21 +11860,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11894,23 +11897,23 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
@@ -11955,7 +11958,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11964,7 +11967,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11976,21 +11979,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12013,16 +12016,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12072,7 +12075,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12090,24 +12093,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12130,16 +12133,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12189,7 +12192,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12198,10 +12201,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12210,21 +12213,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12247,16 +12250,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12306,7 +12309,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12324,10 +12327,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12338,10 +12341,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12453,10 +12456,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12570,10 +12573,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12596,19 +12599,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12657,7 +12660,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12678,21 +12681,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12718,20 +12721,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12755,10 +12758,10 @@
         <v>184</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12776,7 +12779,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12797,21 +12800,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12837,21 +12840,21 @@
         <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12893,7 +12896,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12914,21 +12917,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12954,21 +12957,21 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13010,7 +13013,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13019,7 +13022,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13031,21 +13034,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13071,23 +13074,23 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13129,7 +13132,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13150,21 +13153,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13187,16 +13190,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13246,7 +13249,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13267,10 +13270,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13278,10 +13281,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13304,13 +13307,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13361,7 +13364,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13379,10 +13382,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13393,10 +13396,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13508,10 +13511,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13625,14 +13628,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13654,10 +13657,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13712,7 +13715,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13744,10 +13747,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13773,13 +13776,13 @@
         <v>191</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13809,7 +13812,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13827,7 +13830,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13845,24 +13848,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13888,13 +13891,13 @@
         <v>191</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13920,13 +13923,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13944,7 +13947,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13962,24 +13965,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14002,16 +14005,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14061,7 +14064,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14076,13 +14079,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14093,14 +14096,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14119,16 +14122,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14178,7 +14181,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14199,7 +14202,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14210,10 +14213,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14236,16 +14239,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14295,7 +14298,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14310,13 +14313,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -578,22 +578,22 @@
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -615,22 +615,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -654,10 +654,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -709,7 +709,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -734,10 +734,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -761,7 +761,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
@@ -779,7 +779,7 @@
     <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -794,10 +794,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
@@ -1594,7 +1594,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1879,7 +1879,7 @@
     <t>一部のユニット表現システムのユニットのコンピューター処理可能な形式。 / A computer processable form of the unit in some unit representation system.</t>
   </si>
   <si>
-    <t>優先システムはUCUMですが、スノムCTは（慣習ユニットに）または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するメタデータ / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -572,6 +572,10 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier:rpNumber.use</t>
   </si>
   <si>
@@ -600,6 +604,10 @@
   </si>
   <si>
     <t>Identifier.use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -761,7 +769,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
@@ -4014,7 +4022,7 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4034,10 +4042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4063,16 +4071,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4097,13 +4105,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4121,7 +4129,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4133,7 +4141,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4142,7 +4150,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4153,10 +4161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4179,19 +4187,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4216,13 +4224,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4240,7 +4248,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4252,7 +4260,7 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4261,21 +4269,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4301,23 +4309,23 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4359,7 +4367,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4371,7 +4379,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4380,21 +4388,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4420,13 +4428,13 @@
         <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4476,7 +4484,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4488,7 +4496,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4497,21 +4505,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4534,13 +4542,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4591,7 +4599,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4603,7 +4611,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4612,21 +4620,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4649,16 +4657,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4708,7 +4716,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4720,7 +4728,7 @@
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4729,24 +4737,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4771,13 +4779,13 @@
         <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4859,7 +4867,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>166</v>
@@ -4974,7 +4982,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>173</v>
@@ -5071,7 +5079,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5091,10 +5099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5120,16 +5128,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5154,13 +5162,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5178,7 +5186,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5190,7 +5198,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5199,7 +5207,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5210,10 +5218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5236,19 +5244,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5273,13 +5281,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5297,7 +5305,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5309,7 +5317,7 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5318,21 +5326,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5358,23 +5366,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5416,7 +5424,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5428,7 +5436,7 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5437,21 +5445,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5477,13 +5485,13 @@
         <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5533,7 +5541,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5545,7 +5553,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5554,21 +5562,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5591,13 +5599,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5648,7 +5656,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5660,7 +5668,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5669,21 +5677,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5706,16 +5714,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5765,7 +5773,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5777,7 +5785,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5786,24 +5794,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5828,13 +5836,13 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5916,7 +5924,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>166</v>
@@ -6031,7 +6039,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>173</v>
@@ -6128,7 +6136,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6148,10 +6156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6177,16 +6185,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6211,13 +6219,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6235,7 +6243,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6247,7 +6255,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6256,7 +6264,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6267,10 +6275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6293,19 +6301,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6330,13 +6338,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6354,7 +6362,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6366,7 +6374,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6375,21 +6383,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6415,23 +6423,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6473,7 +6481,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6485,7 +6493,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6494,21 +6502,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6534,13 +6542,13 @@
         <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6590,7 +6598,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6602,7 +6610,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6611,21 +6619,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6648,13 +6656,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6705,7 +6713,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6717,7 +6725,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6726,21 +6734,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6763,16 +6771,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6822,7 +6830,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6834,7 +6842,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6843,21 +6851,21 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6883,13 +6891,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6915,13 +6923,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6939,7 +6947,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6954,16 +6962,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6971,10 +6979,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6997,16 +7005,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7032,13 +7040,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7056,7 +7064,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7071,13 +7079,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7088,10 +7096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7117,13 +7125,13 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7149,13 +7157,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7173,7 +7181,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7188,16 +7196,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7205,10 +7213,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7231,16 +7239,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7270,7 +7278,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7288,7 +7296,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7306,13 +7314,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7320,10 +7328,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7349,13 +7357,13 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7381,13 +7389,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7405,7 +7413,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7420,16 +7428,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7437,10 +7445,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7463,16 +7471,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7522,7 +7530,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7543,7 +7551,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7554,10 +7562,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7580,13 +7588,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7637,7 +7645,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7658,7 +7666,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7669,10 +7677,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7695,16 +7703,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7754,7 +7762,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7769,27 +7777,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7812,16 +7820,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7871,7 +7879,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7886,27 +7894,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7929,16 +7937,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7988,7 +7996,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8003,27 +8011,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8046,16 +8054,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8105,7 +8113,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8120,16 +8128,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8145,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8163,13 +8171,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8220,7 +8228,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8235,27 +8243,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8278,16 +8286,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8337,7 +8345,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8352,16 +8360,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8369,10 +8377,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,16 +8403,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8454,7 +8462,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8469,16 +8477,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8486,10 +8494,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8512,16 +8520,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8547,11 +8555,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8569,7 +8577,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8584,13 +8592,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8601,10 +8609,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8627,16 +8635,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8686,7 +8694,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8707,10 +8715,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8718,10 +8726,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,16 +8752,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8779,13 +8787,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8803,7 +8811,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8818,27 +8826,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,16 +8869,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8920,7 +8928,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8935,16 +8943,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8952,10 +8960,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8978,16 +8986,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9037,7 +9045,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9052,13 +9060,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9069,10 +9077,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9098,13 +9106,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9154,7 +9162,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9175,7 +9183,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9186,10 +9194,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9212,16 +9220,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9271,7 +9279,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9286,13 +9294,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9303,10 +9311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9332,14 +9340,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9388,7 +9396,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9403,13 +9411,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9420,10 +9428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9446,16 +9454,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9481,13 +9489,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9505,7 +9513,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9526,7 +9534,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9537,10 +9545,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,16 +9571,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9622,7 +9630,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9637,13 +9645,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9654,10 +9662,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9680,16 +9688,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9739,7 +9747,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9754,13 +9762,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9771,10 +9779,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9797,16 +9805,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9856,7 +9864,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9868,7 +9876,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9877,7 +9885,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9888,10 +9896,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9914,13 +9922,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9971,7 +9979,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9989,10 +9997,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10003,10 +10011,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10032,10 +10040,10 @@
         <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10118,10 +10126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10147,10 +10155,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10231,13 +10239,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10259,13 +10267,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10325,10 +10333,10 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10348,13 +10356,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10376,13 +10384,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10442,10 +10450,10 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10465,14 +10473,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10494,10 +10502,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10552,7 +10560,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10584,10 +10592,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10610,16 +10618,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10669,7 +10677,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10690,7 +10698,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10701,10 +10709,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10816,10 +10824,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10933,14 +10941,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10962,10 +10970,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11020,7 +11028,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11060,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11078,16 +11086,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11137,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11146,10 +11154,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11158,21 +11166,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11195,16 +11203,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11254,7 +11262,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11275,7 +11283,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11286,10 +11294,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11312,16 +11320,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11371,7 +11379,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11392,7 +11400,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11411,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11429,19 +11437,19 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11490,7 +11498,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11508,10 +11516,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11522,10 +11530,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11637,10 +11645,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11734,7 +11742,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11754,10 +11762,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11780,16 +11788,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11839,7 +11847,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11848,10 +11856,10 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11860,21 +11868,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11897,23 +11905,23 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
@@ -11958,7 +11966,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11967,10 +11975,10 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -11979,21 +11987,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12016,16 +12024,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12075,7 +12083,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12093,24 +12101,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12133,16 +12141,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12192,7 +12200,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12201,10 +12209,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12213,21 +12221,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12250,16 +12258,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12309,7 +12317,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12327,10 +12335,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12341,10 +12349,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12456,10 +12464,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12553,7 +12561,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12573,10 +12581,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12599,19 +12607,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12660,7 +12668,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12672,7 +12680,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12681,21 +12689,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12721,20 +12729,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12755,13 +12763,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12779,7 +12787,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12791,7 +12799,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12800,21 +12808,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12840,21 +12848,21 @@
         <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12896,7 +12904,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12908,7 +12916,7 @@
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12917,21 +12925,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12957,21 +12965,21 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13013,7 +13021,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13022,10 +13030,10 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13034,21 +13042,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13074,23 +13082,23 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13132,7 +13140,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13144,7 +13152,7 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13153,21 +13161,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13190,16 +13198,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13249,7 +13257,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13270,10 +13278,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13281,10 +13289,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13307,13 +13315,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13364,7 +13372,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13382,10 +13390,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13396,10 +13404,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13511,10 +13519,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13628,14 +13636,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13657,10 +13665,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13715,7 +13723,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13747,10 +13755,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13773,16 +13781,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13812,7 +13820,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13830,7 +13838,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13848,24 +13856,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13888,16 +13896,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13923,13 +13931,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13947,7 +13955,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13965,24 +13973,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14005,16 +14013,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14064,7 +14072,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14079,13 +14087,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14096,14 +14104,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14122,16 +14130,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14181,7 +14189,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14202,7 +14210,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14213,10 +14221,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14239,16 +14247,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14298,7 +14306,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14313,13 +14321,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -572,10 +572,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier:rpNumber.use</t>
   </si>
   <si>
@@ -604,10 +600,6 @@
   </si>
   <si>
     <t>Identifier.use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -769,7 +761,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
@@ -4022,7 +4014,7 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4042,10 +4034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4071,16 +4063,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4105,52 +4097,52 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4161,10 +4153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4187,19 +4179,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4224,66 +4216,66 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4309,100 +4301,100 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="S17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4428,13 +4420,13 @@
         <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4484,42 +4476,42 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4542,13 +4534,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4599,42 +4591,42 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4657,16 +4649,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4716,45 +4708,45 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4779,13 +4771,13 @@
         <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4867,7 +4859,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>166</v>
@@ -4982,7 +4974,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>173</v>
@@ -5079,7 +5071,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5099,10 +5091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5128,16 +5120,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5162,52 +5154,52 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5218,10 +5210,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5244,19 +5236,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5281,66 +5273,66 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5366,23 +5358,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5424,42 +5416,42 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5485,13 +5477,13 @@
         <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5541,42 +5533,42 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5599,13 +5591,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5656,42 +5648,42 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5714,16 +5706,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5773,45 +5765,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5836,13 +5828,13 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5924,7 +5916,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>166</v>
@@ -6039,7 +6031,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>173</v>
@@ -6136,7 +6128,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6156,10 +6148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6185,16 +6177,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6219,52 +6211,52 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6275,10 +6267,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6301,19 +6293,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6338,66 +6330,66 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Z34" t="s" s="2">
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6423,23 +6415,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6481,42 +6473,42 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6542,13 +6534,13 @@
         <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6598,42 +6590,42 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6656,13 +6648,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6713,42 +6705,42 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6771,16 +6763,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6830,42 +6822,42 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6891,13 +6883,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6923,13 +6915,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6947,7 +6939,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6962,16 +6954,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6979,10 +6971,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7005,16 +6997,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7040,14 +7032,14 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Y40" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7064,7 +7056,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7079,13 +7071,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7096,10 +7088,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7125,13 +7117,13 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7157,13 +7149,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7181,7 +7173,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7196,16 +7188,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7213,10 +7205,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7239,16 +7231,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7278,7 +7270,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7296,7 +7288,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7314,13 +7306,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7328,10 +7320,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7357,13 +7349,13 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7389,13 +7381,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7413,7 +7405,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7428,16 +7420,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7445,10 +7437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7471,16 +7463,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7530,7 +7522,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7551,7 +7543,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7562,10 +7554,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7588,13 +7580,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7645,7 +7637,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7666,7 +7658,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7677,10 +7669,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7703,16 +7695,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7762,7 +7754,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7777,27 +7769,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7820,16 +7812,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7879,7 +7871,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7894,27 +7886,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7937,16 +7929,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7996,7 +7988,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8011,27 +8003,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL48" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8054,16 +8046,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8113,7 +8105,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8128,16 +8120,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8145,10 +8137,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8171,13 +8163,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8228,7 +8220,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8243,27 +8235,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8286,16 +8278,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8345,7 +8337,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8360,16 +8352,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8377,10 +8369,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8403,16 +8395,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8462,7 +8454,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8477,16 +8469,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8494,10 +8486,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8520,16 +8512,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8555,11 +8547,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8577,7 +8569,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8592,13 +8584,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8609,10 +8601,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8635,16 +8627,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L54" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8694,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8715,10 +8707,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8726,10 +8718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8752,16 +8744,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8787,13 +8779,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8811,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8826,27 +8818,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8869,16 +8861,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8928,7 +8920,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8943,16 +8935,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8960,10 +8952,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8986,16 +8978,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9045,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9060,13 +9052,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9077,10 +9069,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9106,13 +9098,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9162,7 +9154,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9183,7 +9175,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9194,10 +9186,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9220,16 +9212,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9279,7 +9271,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9294,13 +9286,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9311,10 +9303,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9340,14 +9332,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9396,7 +9388,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9411,13 +9403,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9428,10 +9420,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9454,16 +9446,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9489,13 +9481,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9513,7 +9505,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9534,7 +9526,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9545,10 +9537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9571,16 +9563,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9630,7 +9622,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9645,13 +9637,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9662,10 +9654,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9688,16 +9680,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9747,7 +9739,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9762,13 +9754,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9779,10 +9771,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9805,16 +9797,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9864,7 +9856,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9876,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9885,7 +9877,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9896,10 +9888,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9922,13 +9914,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9979,7 +9971,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9997,10 +9989,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10011,10 +10003,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10040,10 +10032,10 @@
         <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10126,10 +10118,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10155,10 +10147,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10239,13 +10231,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10267,13 +10259,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10333,10 +10325,10 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10356,13 +10348,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10384,13 +10376,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10450,10 +10442,10 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10473,14 +10465,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10502,10 +10494,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10560,7 +10552,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10592,10 +10584,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10618,16 +10610,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10677,7 +10669,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10698,7 +10690,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10709,10 +10701,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10824,10 +10816,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10941,14 +10933,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10970,10 +10962,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11028,7 +11020,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11060,10 +11052,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11086,16 +11078,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11145,7 +11137,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11154,33 +11146,33 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AJ75" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11203,16 +11195,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L76" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11262,7 +11254,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11283,7 +11275,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11294,10 +11286,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11320,16 +11312,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11379,7 +11371,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11400,7 +11392,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11411,10 +11403,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11437,19 +11429,19 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11498,7 +11490,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11516,10 +11508,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11530,10 +11522,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11645,10 +11637,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11742,7 +11734,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11762,10 +11754,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11788,16 +11780,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11847,42 +11839,42 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>529</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11905,103 +11897,103 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>537</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12024,16 +12016,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12083,7 +12075,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12101,24 +12093,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>545</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12141,16 +12133,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12200,7 +12192,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12209,33 +12201,33 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12258,16 +12250,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12317,7 +12309,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12335,10 +12327,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12349,10 +12341,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12464,10 +12456,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12561,7 +12553,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12581,10 +12573,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12607,19 +12599,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12668,42 +12660,42 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12729,100 +12721,100 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y89" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="P89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q89" t="s" s="2">
+      <c r="Z89" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="R89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>575</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12848,98 +12840,98 @@
         <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="S90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>583</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12965,98 +12957,98 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI91" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
+      <c r="AJ91" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13082,100 +13074,100 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="S92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>599</v>
-      </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13198,16 +13190,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L93" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>603</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13257,7 +13249,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13278,10 +13270,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13289,10 +13281,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13315,13 +13307,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13372,7 +13364,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13390,10 +13382,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13404,10 +13396,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13519,10 +13511,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13636,14 +13628,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13665,10 +13657,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13723,7 +13715,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13755,10 +13747,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13781,16 +13773,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13820,7 +13812,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13838,7 +13830,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13856,24 +13848,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13896,16 +13888,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13931,13 +13923,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13955,7 +13947,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13973,24 +13965,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14013,16 +14005,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L100" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14072,7 +14064,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14087,13 +14079,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14104,14 +14096,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14130,16 +14122,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14189,7 +14181,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14210,7 +14202,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14221,10 +14213,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14247,16 +14239,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14306,7 +14298,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14321,13 +14313,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -491,7 +491,15 @@
 このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
-    <t>これは業務IDであって、リソースに対するIDではない。</t>
+    <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
+Slice定義は下記のようになる。  
+[Sliceで定義される識別子]  
+　- rpNumber : 処方箋内部の剤グループとしてのRp番号  
+　- orderInRp : 同一RP番号（剤グループ）での薬剤の表記順  
+　- requestIdentifier : 処方オーダに対するID  
+　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
+[invariantで定義される識別子]  
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -501,6 +509,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -749,100 +761,100 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
+    <t>MedicationRequest.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon</t>
+  </si>
+  <si>
+    <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
     <t>処方箋に対するID</t>
   </si>
   <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
-  </si>
-  <si>
-    <t>identifier値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.system</t>
   </si>
   <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2350,7 +2362,7 @@
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3663,33 +3675,33 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3714,13 +3726,13 @@
         <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3785,27 +3797,27 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3828,13 +3840,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3885,7 +3897,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3906,7 +3918,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3917,10 +3929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3949,7 +3961,7 @@
         <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>140</v>
@@ -3990,10 +4002,10 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -4002,7 +4014,7 @@
         <v>154</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4023,7 +4035,7 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -4034,10 +4046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4063,16 +4075,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4097,13 +4109,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4121,7 +4133,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4142,7 +4154,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4153,10 +4165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4179,19 +4191,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4216,13 +4228,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4240,7 +4252,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4261,21 +4273,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4301,23 +4313,23 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4359,7 +4371,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4380,21 +4392,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4417,16 +4429,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4476,7 +4488,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4497,21 +4509,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4534,13 +4546,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4591,7 +4603,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4612,21 +4624,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4649,16 +4661,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4708,7 +4720,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4729,24 +4741,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4756,7 +4768,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4771,13 +4783,13 @@
         <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4842,27 +4854,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4885,13 +4897,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4942,7 +4954,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4963,7 +4975,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4974,10 +4986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5006,7 +5018,7 @@
         <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>140</v>
@@ -5047,10 +5059,10 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
@@ -5059,7 +5071,7 @@
         <v>154</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5080,7 +5092,7 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5091,10 +5103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5120,16 +5132,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5154,13 +5166,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5178,7 +5190,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5199,7 +5211,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5210,10 +5222,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5236,19 +5248,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5273,13 +5285,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5297,7 +5309,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5318,21 +5330,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5358,23 +5370,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5416,7 +5428,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5437,21 +5449,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5474,16 +5486,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5533,7 +5545,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5554,21 +5566,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5591,13 +5603,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5648,7 +5660,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5669,21 +5681,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5706,16 +5718,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5765,7 +5777,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5786,24 +5798,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5813,7 +5825,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5828,13 +5840,13 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5899,27 +5911,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5942,13 +5954,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5999,7 +6011,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6020,7 +6032,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6031,10 +6043,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6063,7 +6075,7 @@
         <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>140</v>
@@ -6104,10 +6116,10 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6116,7 +6128,7 @@
         <v>154</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6137,7 +6149,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6148,10 +6160,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6177,16 +6189,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6211,13 +6223,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6235,7 +6247,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6256,7 +6268,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6267,10 +6279,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6293,19 +6305,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6330,13 +6342,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6354,7 +6366,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6375,21 +6387,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6415,23 +6427,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6473,7 +6485,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6494,21 +6506,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6531,16 +6543,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6590,7 +6602,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6611,21 +6623,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6648,13 +6660,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6705,7 +6717,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6726,21 +6738,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6763,16 +6775,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6822,7 +6834,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6843,21 +6855,21 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6883,13 +6895,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6915,13 +6927,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6939,7 +6951,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6954,16 +6966,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6971,10 +6983,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6997,16 +7009,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7032,13 +7044,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7056,7 +7068,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7071,13 +7083,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7088,10 +7100,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7117,13 +7129,13 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7149,13 +7161,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7173,7 +7185,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7188,16 +7200,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7205,10 +7217,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7231,16 +7243,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7270,7 +7282,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7288,7 +7300,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7306,13 +7318,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7320,10 +7332,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7349,13 +7361,13 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7381,13 +7393,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7405,7 +7417,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7420,16 +7432,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7437,10 +7449,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7463,16 +7475,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7522,7 +7534,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7543,7 +7555,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7554,10 +7566,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7580,13 +7592,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7637,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7658,7 +7670,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7669,10 +7681,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7695,16 +7707,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7754,7 +7766,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7769,27 +7781,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7812,16 +7824,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7871,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7886,27 +7898,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7929,16 +7941,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7988,7 +8000,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8003,27 +8015,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8046,16 +8058,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8105,7 +8117,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8120,16 +8132,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8163,13 +8175,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8220,7 +8232,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8235,27 +8247,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8278,16 +8290,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8337,7 +8349,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8352,16 +8364,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8369,10 +8381,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,16 +8407,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8454,7 +8466,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8469,16 +8481,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8486,10 +8498,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8512,16 +8524,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8547,11 +8559,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8569,7 +8581,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8584,13 +8596,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8601,10 +8613,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8627,16 +8639,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8686,7 +8698,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8707,10 +8719,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8718,10 +8730,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,16 +8756,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8779,13 +8791,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8803,7 +8815,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8818,27 +8830,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,16 +8873,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8920,7 +8932,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8935,16 +8947,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8952,10 +8964,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8978,16 +8990,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9037,7 +9049,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9052,13 +9064,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9069,10 +9081,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9098,13 +9110,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9154,7 +9166,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9175,7 +9187,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9186,10 +9198,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9212,16 +9224,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9271,7 +9283,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9286,13 +9298,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9303,10 +9315,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9332,14 +9344,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9388,7 +9400,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9403,13 +9415,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9420,10 +9432,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9446,16 +9458,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9481,13 +9493,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9505,7 +9517,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9526,7 +9538,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9537,10 +9549,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,16 +9575,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9622,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9637,13 +9649,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9654,10 +9666,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9680,16 +9692,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9739,7 +9751,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9754,13 +9766,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9771,10 +9783,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9797,16 +9809,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9856,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9877,7 +9889,7 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9888,10 +9900,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9914,13 +9926,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9971,7 +9983,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9989,10 +10001,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10003,10 +10015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10029,13 +10041,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10086,7 +10098,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10107,7 +10119,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10118,10 +10130,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10147,10 +10159,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10189,7 +10201,7 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
@@ -10199,7 +10211,7 @@
         <v>154</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10231,13 +10243,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10259,13 +10271,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10316,7 +10328,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10325,7 +10337,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10348,13 +10360,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10376,13 +10388,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10433,7 +10445,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10442,7 +10454,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10465,14 +10477,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10494,10 +10506,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10552,7 +10564,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10584,10 +10596,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10610,16 +10622,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10669,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10690,7 +10702,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10701,10 +10713,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10727,13 +10739,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10784,7 +10796,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10805,7 +10817,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10816,10 +10828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10848,7 +10860,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10901,7 +10913,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10922,7 +10934,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -10933,14 +10945,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10962,10 +10974,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11020,7 +11032,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11052,10 +11064,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11078,16 +11090,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11137,7 +11149,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11146,10 +11158,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11158,21 +11170,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11195,16 +11207,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11254,7 +11266,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11275,7 +11287,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11286,10 +11298,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11312,16 +11324,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11371,7 +11383,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11392,7 +11404,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11429,19 +11441,19 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11490,7 +11502,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11508,10 +11520,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11522,10 +11534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11548,13 +11560,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11605,7 +11617,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11626,7 +11638,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11637,10 +11649,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11669,7 +11681,7 @@
         <v>138</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>140</v>
@@ -11710,10 +11722,10 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
@@ -11722,7 +11734,7 @@
         <v>154</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11743,7 +11755,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11754,10 +11766,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11780,16 +11792,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11839,7 +11851,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11848,7 +11860,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11860,21 +11872,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11897,23 +11909,23 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
@@ -11958,7 +11970,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11967,7 +11979,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11979,21 +11991,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12016,16 +12028,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12075,7 +12087,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12093,24 +12105,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12133,16 +12145,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12192,7 +12204,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12201,10 +12213,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12213,21 +12225,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12250,16 +12262,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12309,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12327,10 +12339,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12341,10 +12353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12367,13 +12379,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12424,7 +12436,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12445,7 +12457,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12456,10 +12468,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12488,7 +12500,7 @@
         <v>138</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>140</v>
@@ -12529,10 +12541,10 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
@@ -12541,7 +12553,7 @@
         <v>154</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12562,7 +12574,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12573,10 +12585,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12599,19 +12611,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12660,7 +12672,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12681,21 +12693,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12721,20 +12733,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12755,13 +12767,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12779,7 +12791,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12800,21 +12812,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12837,24 +12849,24 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12896,7 +12908,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12917,21 +12929,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12957,21 +12969,21 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13013,7 +13025,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13022,7 +13034,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13034,21 +13046,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13074,23 +13086,23 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13132,7 +13144,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13153,21 +13165,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13190,16 +13202,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13249,7 +13261,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13270,10 +13282,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13281,10 +13293,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13307,13 +13319,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13364,7 +13376,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13382,10 +13394,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13396,10 +13408,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13422,13 +13434,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13479,7 +13491,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13500,7 +13512,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13511,10 +13523,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13543,7 +13555,7 @@
         <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>140</v>
@@ -13596,7 +13608,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13617,7 +13629,7 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13628,14 +13640,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13657,10 +13669,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13715,7 +13727,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13747,10 +13759,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13773,16 +13785,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13812,7 +13824,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13830,7 +13842,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13848,24 +13860,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13888,16 +13900,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13923,13 +13935,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13947,7 +13959,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13965,24 +13977,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14005,16 +14017,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14064,7 +14076,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14079,13 +14091,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14096,14 +14108,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14122,16 +14134,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14181,7 +14193,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14202,7 +14214,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14213,10 +14225,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14239,16 +14251,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14298,7 +14310,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14313,13 +14325,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="650">
   <si>
     <t>Property</t>
   </si>
@@ -1466,13 +1466,19 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>薬をどのように服用すべきか / How the medication should be taken</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>薬の要求には、経口投与または静脈内または筋肉内の用量のオプションが含まれる場合があります。たとえば、「吐き気に必要に応じて、1日に2回Ondansetron 8mgまたはIV」または「Compazine®（プロクロロペラジン）5-10mg POまたは25mg PR BID PRN吐き気または嘔吐」。これらの場合、グループ化できる2つの投薬要求が作成されます。使用する投与経路の決定は、用量が必要な時点での患者の状態に基づいています。 / There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>see dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1606,14 +1612,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>Supply.quantity[moodCode=RQO]</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
@@ -1749,6 +1748,15 @@
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
@@ -9815,10 +9823,10 @@
         <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9883,13 +9891,13 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9900,10 +9908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9926,13 +9934,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9983,7 +9991,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10001,10 +10009,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10015,10 +10023,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10044,10 +10052,10 @@
         <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10130,10 +10138,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10159,10 +10167,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10243,13 +10251,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10271,13 +10279,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10337,7 +10345,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10360,13 +10368,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10388,13 +10396,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10454,7 +10462,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10477,14 +10485,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10506,10 +10514,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10564,7 +10572,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10596,10 +10604,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10622,16 +10630,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10681,7 +10689,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10702,7 +10710,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10713,10 +10721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10828,10 +10836,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10945,14 +10953,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10974,10 +10982,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11032,7 +11040,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11064,10 +11072,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11090,16 +11098,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11149,7 +11157,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11158,10 +11166,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>501</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11170,13 +11178,13 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
@@ -11216,7 +11224,7 @@
         <v>507</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11333,7 +11341,7 @@
         <v>511</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12145,7 +12153,7 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>546</v>
@@ -12154,7 +12162,7 @@
         <v>547</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12213,33 +12221,33 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>501</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>502</v>
+        <v>549</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>503</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12265,13 +12273,13 @@
         <v>505</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12321,7 +12329,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12339,10 +12347,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12353,10 +12361,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12468,10 +12476,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12585,10 +12593,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12611,19 +12619,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12672,7 +12680,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12693,21 +12701,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12733,20 +12741,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12770,10 +12778,10 @@
         <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12791,7 +12799,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12812,21 +12820,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12852,21 +12860,21 @@
         <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12908,7 +12916,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12929,21 +12937,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12969,21 +12977,21 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13025,7 +13033,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13034,7 +13042,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13046,21 +13054,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13086,23 +13094,23 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13144,7 +13152,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13165,21 +13173,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13202,13 +13210,13 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>356</v>
@@ -13261,7 +13269,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13282,7 +13290,7 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>393</v>
@@ -13293,10 +13301,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13319,13 +13327,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13376,7 +13384,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13394,10 +13402,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13408,10 +13416,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13523,10 +13531,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13640,14 +13648,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13669,10 +13677,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13727,7 +13735,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13759,10 +13767,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13788,13 +13796,13 @@
         <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13824,25 +13832,25 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13860,24 +13868,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13903,13 +13911,13 @@
         <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13938,10 +13946,10 @@
         <v>282</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13959,7 +13967,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13977,24 +13985,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14017,13 +14025,13 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>356</v>
@@ -14076,7 +14084,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14091,13 +14099,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14108,14 +14116,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14134,16 +14142,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14193,7 +14201,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14214,7 +14222,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14225,10 +14233,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14251,16 +14259,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14310,7 +14318,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14325,13 +14333,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -1814,7 +1814,7 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1826,7 +1826,7 @@
     <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -824,7 +824,7 @@
     <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
-    <t>処方箋に対するID</t>
+    <t>全国で⼀意となる処方箋ID</t>
   </si>
   <si>
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -1017,8 +1017,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
   </si>
   <si>
     <t>初期記録にはない報告</t>
@@ -1045,7 +1045,7 @@
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
 ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
-厚生労働省標準であるHOT9コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
+厚生労働省標準であるHOT9コード、HOT13コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
 なお、上記のいずれの標準的コードも付番されていない医薬品や医療材料の場合には、薬機法の下で使用されているGS1標準の識別コードであるGTIN(Global Trade Item Number)の調剤包装単位（最少包装単位、個別包装単位）14桁を使用する。  
 ひとつの処方薬、医療材料を複数のコード体系のコードで記述してもよく、その場合にcoding 要素を繰り返して記述する。  
 ただし、ひとつの処方薬を複数のコードで繰り返し記述する場合には、それらのコードが指し示す処方薬、医療材料は当然同一でなければならない。  
@@ -1166,7 +1166,7 @@
 </t>
   </si>
   <si>
-    <t>この処方オーダが最初に記述された日</t>
+    <t>この処方オーダが最初に記述された日時</t>
   </si>
   <si>
     <t>JP Coreでは必須。処方指示が最初に作成された日時。秒の精度まで記録する。タイムゾーンも付与しなければならない。</t>
@@ -1360,7 +1360,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -2368,17 +2368,17 @@
   <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2387,27 +2387,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="178.55859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3852" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -855,6 +855,18 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:other</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>このリクエストの外部ID / External ids for this request</t>
+  </si>
+  <si>
+    <t>ビジネスプロセスによって定義されるこの薬物療法要求に関連付けられたidentifier、および/またはリソース自体への直接のURL参照が適切でない場合にそれを参照するために使用されるidentifier。これらは、パフォーマーまたは他のシステムによってこのリソースに割り当てられたビジネスidentifierであり、リソースが更新され、サーバーからサーバーに伝播するため、一定のままです。 / Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2365,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO102"/>
+  <dimension ref="A1:AO103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -6877,39 +6889,41 @@
         <v>269</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6935,13 +6949,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6959,13 +6973,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6974,27 +6988,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>276</v>
+        <v>157</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>277</v>
+        <v>158</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>278</v>
+        <v>159</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7002,7 +7016,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -7011,22 +7025,22 @@
         <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7052,13 +7066,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>282</v>
+        <v>185</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7076,10 +7090,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -7091,16 +7105,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7108,10 +7122,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7119,7 +7133,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7128,22 +7142,22 @@
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7169,13 +7183,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7193,10 +7207,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>91</v>
@@ -7208,16 +7222,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7225,10 +7239,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7236,31 +7250,31 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7286,11 +7300,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7308,13 +7324,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7323,16 +7339,16 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7340,10 +7356,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7354,7 +7370,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7363,19 +7379,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7401,13 +7417,11 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7425,13 +7439,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7440,16 +7454,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7457,10 +7471,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7477,22 +7491,22 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7518,13 +7532,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7542,7 +7556,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7557,16 +7571,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7574,10 +7588,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7594,21 +7608,23 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7657,7 +7673,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7678,7 +7694,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7689,10 +7705,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7700,7 +7716,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7715,17 +7731,15 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>327</v>
-      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7774,10 +7788,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7789,27 +7803,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7832,16 +7846,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7891,7 +7905,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7906,27 +7920,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7934,7 +7948,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -7946,19 +7960,19 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8008,10 +8022,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -8023,27 +8037,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8054,7 +8068,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8066,16 +8080,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8125,13 +8139,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8140,27 +8154,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8168,10 +8182,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8180,18 +8194,20 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8240,13 +8256,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8255,27 +8271,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8283,7 +8299,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>91</v>
@@ -8298,17 +8314,15 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8357,7 +8371,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8372,27 +8386,27 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8412,19 +8426,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8474,7 +8488,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8489,16 +8503,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8506,10 +8520,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8529,19 +8543,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>192</v>
+        <v>379</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8567,11 +8581,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8589,7 +8605,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8604,16 +8620,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8621,10 +8637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8644,19 +8660,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>389</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8682,13 +8698,11 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8706,7 +8720,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8721,16 +8735,16 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8738,10 +8752,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8752,7 +8766,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8764,16 +8778,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>393</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="N55" t="s" s="2">
-        <v>397</v>
+        <v>360</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8799,13 +8813,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8823,13 +8837,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8838,27 +8852,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8881,16 +8895,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>406</v>
+        <v>192</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8916,13 +8930,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8940,7 +8954,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8955,27 +8969,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>276</v>
+        <v>405</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8995,19 +9009,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9057,7 +9071,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9072,16 +9086,16 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9089,10 +9103,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9115,16 +9129,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9174,7 +9188,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9189,13 +9203,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9206,10 +9220,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9232,16 +9246,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>423</v>
+        <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9291,7 +9305,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9306,13 +9320,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9323,10 +9337,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9337,7 +9351,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9349,18 +9363,18 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>149</v>
+        <v>427</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>431</v>
-      </c>
+      <c r="N60" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9408,13 +9422,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9423,13 +9437,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9440,10 +9454,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9463,21 +9477,21 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9501,13 +9515,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9525,7 +9539,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9540,13 +9554,13 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9557,10 +9571,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9571,7 +9585,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9583,16 +9597,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>442</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>356</v>
+        <v>441</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9618,13 +9632,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9642,13 +9656,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9657,13 +9671,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9674,10 +9688,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9700,16 +9714,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>451</v>
+        <v>360</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9759,7 +9773,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9774,13 +9788,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9791,10 +9805,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9817,16 +9831,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9876,7 +9890,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9891,13 +9905,13 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9908,10 +9922,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9922,7 +9936,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9934,15 +9948,17 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9991,13 +10007,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10006,13 +10022,13 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10023,10 +10039,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10049,13 +10065,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>168</v>
+        <v>467</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10106,7 +10122,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>171</v>
+        <v>466</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10118,16 +10134,16 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>172</v>
+        <v>471</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10138,10 +10154,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10152,7 +10168,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10164,13 +10180,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10209,29 +10225,31 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10240,7 +10258,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10251,14 +10269,12 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C68" t="s" s="2">
         <v>475</v>
       </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10279,13 +10295,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10324,16 +10340,14 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>178</v>
@@ -10345,7 +10359,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10368,13 +10382,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10384,7 +10398,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10396,13 +10410,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10462,7 +10476,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10485,33 +10499,35 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C70" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="B70" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>137</v>
+        <v>486</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>487</v>
@@ -10519,12 +10535,8 @@
       <c r="M70" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N70" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10572,7 +10584,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>489</v>
+        <v>178</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10581,7 +10593,7 @@
         <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>142</v>
@@ -10593,7 +10605,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10604,33 +10616,33 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>463</v>
+        <v>137</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>491</v>
@@ -10639,9 +10651,11 @@
         <v>492</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10689,19 +10703,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10710,7 +10724,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>494</v>
+        <v>134</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10721,10 +10735,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10747,15 +10761,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>168</v>
+        <v>467</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>169</v>
+        <v>495</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10804,7 +10820,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>171</v>
+        <v>494</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10816,7 +10832,7 @@
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10825,7 +10841,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>172</v>
+        <v>498</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10836,21 +10852,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10862,17 +10878,15 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10921,19 +10935,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10953,14 +10967,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>486</v>
+        <v>136</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10973,26 +10987,24 @@
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>487</v>
+        <v>138</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>488</v>
+        <v>175</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O74" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11040,7 +11052,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>489</v>
+        <v>178</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11061,7 +11073,7 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11072,44 +11084,46 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>499</v>
+        <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11157,19 +11171,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11178,7 +11192,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>503</v>
+        <v>134</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11189,10 +11203,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11215,16 +11229,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11274,7 +11288,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11295,7 +11309,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11306,10 +11320,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11332,7 +11346,7 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>510</v>
@@ -11341,7 +11355,7 @@
         <v>511</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11391,7 +11405,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11412,7 +11426,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11423,10 +11437,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11449,20 +11463,18 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>222</v>
+        <v>509</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11510,7 +11522,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11528,10 +11540,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11542,10 +11554,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11568,16 +11580,20 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>169</v>
+        <v>517</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11625,7 +11641,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>171</v>
+        <v>516</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11637,16 +11653,16 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>172</v>
+        <v>522</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11657,21 +11673,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11683,17 +11699,15 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11730,31 +11744,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11774,21 +11788,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11797,19 +11811,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>360</v>
+        <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>522</v>
+        <v>138</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>523</v>
+        <v>175</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>524</v>
+        <v>140</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11847,31 +11861,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>525</v>
+        <v>178</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11880,21 +11894,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>527</v>
+        <v>172</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11917,24 +11931,22 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" t="s" s="2">
-        <v>533</v>
-      </c>
+      <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
         <v>82</v>
       </c>
@@ -11978,7 +11990,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11987,7 +11999,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11999,21 +12011,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12033,25 +12045,27 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>538</v>
+        <v>364</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="R83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12095,7 +12109,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12104,7 +12118,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -12113,24 +12127,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12153,16 +12167,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>499</v>
+        <v>542</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>502</v>
+        <v>545</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12212,7 +12226,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12230,24 +12244,24 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12270,16 +12284,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>554</v>
+        <v>506</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12329,7 +12343,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12347,24 +12361,24 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12387,15 +12401,17 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>168</v>
+        <v>509</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>169</v>
+        <v>556</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12444,7 +12460,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>171</v>
+        <v>555</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12456,16 +12472,16 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>172</v>
+        <v>560</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12476,21 +12492,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12502,17 +12518,15 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12549,31 +12563,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12593,21 +12607,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12616,23 +12630,21 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>560</v>
+        <v>137</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>561</v>
+        <v>138</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>562</v>
+        <v>175</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12668,31 +12680,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>565</v>
+        <v>178</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12701,21 +12713,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>566</v>
+        <v>172</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12732,74 +12744,74 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>564</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q89" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="R89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12820,21 +12832,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12851,30 +12863,32 @@
         <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="R90" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12892,13 +12906,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -12916,7 +12930,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12937,21 +12951,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12974,24 +12988,24 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13033,7 +13047,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13042,7 +13056,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13054,21 +13068,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13091,26 +13105,24 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13152,7 +13164,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13161,7 +13173,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -13173,21 +13185,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13207,27 +13219,29 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>603</v>
+        <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>82</v>
@@ -13269,7 +13283,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13290,21 +13304,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13327,7 +13341,7 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>463</v>
+        <v>607</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>608</v>
@@ -13335,7 +13349,9 @@
       <c r="M94" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N94" s="2"/>
+      <c r="N94" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13384,7 +13400,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13402,13 +13418,13 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="AM94" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="AN94" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13416,10 +13432,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13442,13 +13458,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>168</v>
+        <v>467</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>169</v>
+        <v>612</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
+        <v>613</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13499,7 +13515,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>171</v>
+        <v>611</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13511,16 +13527,16 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>172</v>
+        <v>615</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13531,21 +13547,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13557,17 +13573,15 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13616,19 +13630,19 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13648,14 +13662,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>486</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13668,26 +13682,24 @@
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>487</v>
+        <v>138</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>488</v>
+        <v>175</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O97" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13735,7 +13747,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>489</v>
+        <v>178</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13756,7 +13768,7 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
@@ -13767,44 +13779,46 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>608</v>
+        <v>491</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>616</v>
+        <v>492</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13828,11 +13842,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13850,42 +13866,42 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>615</v>
+        <v>493</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>619</v>
+        <v>134</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13893,7 +13909,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>91</v>
@@ -13911,13 +13927,13 @@
         <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13943,13 +13959,11 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13967,10 +13981,10 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>91</v>
@@ -13985,24 +13999,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14025,16 +14039,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>631</v>
+        <v>192</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>356</v>
+        <v>628</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14060,13 +14074,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14084,7 +14098,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14099,38 +14113,38 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14142,16 +14156,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>641</v>
+        <v>360</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14201,13 +14215,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14216,13 +14230,13 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14233,14 +14247,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14259,16 +14273,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14318,7 +14332,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14333,18 +14347,135 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K103" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
+      <c r="L103" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="AN102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO102" t="s" s="2">
+      <c r="M103" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3852" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="650">
   <si>
     <t>Property</t>
   </si>
@@ -855,18 +855,6 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:other</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>このリクエストの外部ID / External ids for this request</t>
-  </si>
-  <si>
-    <t>ビジネスプロセスによって定義されるこの薬物療法要求に関連付けられたidentifier、および/またはリソース自体への直接のURL参照が適切でない場合にそれを参照するために使用されるidentifier。これらは、パフォーマーまたは他のシステムによってこのリソースに割り当てられたビジネスidentifierであり、リソースが更新され、サーバーからサーバーに伝播するため、一定のままです。 / Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2377,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO103"/>
+  <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -6889,41 +6877,39 @@
         <v>269</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6949,13 +6935,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6973,13 +6959,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>148</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6988,27 +6974,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>156</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>157</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7016,7 +7002,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -7025,22 +7011,22 @@
         <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7066,13 +7052,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7090,10 +7076,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -7105,16 +7091,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7122,10 +7108,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7133,7 +7119,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -7142,22 +7128,22 @@
         <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7183,34 +7169,34 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>286</v>
+        <v>185</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>91</v>
@@ -7222,16 +7208,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7239,10 +7225,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7250,31 +7236,31 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7300,37 +7286,35 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AG42" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7339,16 +7323,16 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7356,10 +7340,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7370,7 +7354,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7379,19 +7363,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7417,11 +7401,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7439,13 +7425,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7454,16 +7440,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7471,10 +7457,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7491,22 +7477,22 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>111</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7532,31 +7518,31 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7571,16 +7557,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7588,10 +7574,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7608,23 +7594,21 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7673,7 +7657,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7694,7 +7678,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7705,10 +7689,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7716,7 +7700,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7731,15 +7715,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7788,10 +7774,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7803,27 +7789,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7846,16 +7832,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7905,7 +7891,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7920,27 +7906,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7948,7 +7934,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -7960,19 +7946,19 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8022,10 +8008,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>91</v>
@@ -8037,27 +8023,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>343</v>
+        <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8068,7 +8054,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8080,16 +8066,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8139,13 +8125,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8154,27 +8140,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8182,10 +8168,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8194,20 +8180,18 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8256,13 +8240,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8271,27 +8255,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8299,7 +8283,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>91</v>
@@ -8314,15 +8298,17 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8371,7 +8357,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8386,27 +8372,27 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8426,19 +8412,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8488,7 +8474,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8503,16 +8489,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8520,10 +8506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8543,19 +8529,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>379</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8581,13 +8567,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8605,7 +8589,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8620,16 +8604,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8637,10 +8621,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8660,19 +8644,19 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8698,11 +8682,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8720,7 +8706,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8735,16 +8721,16 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8752,10 +8738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8766,7 +8752,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8778,16 +8764,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>393</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8813,13 +8799,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8837,13 +8823,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8852,27 +8838,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8895,16 +8881,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8930,13 +8916,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8954,7 +8940,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8969,27 +8955,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>405</v>
+        <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9009,19 +8995,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9071,7 +9057,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9086,16 +9072,16 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9103,10 +9089,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9129,16 +9115,16 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9188,7 +9174,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9203,13 +9189,13 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9220,10 +9206,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9246,16 +9232,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>105</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>425</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9305,7 +9291,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9320,13 +9306,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9337,10 +9323,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9351,7 +9337,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9363,18 +9349,18 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>427</v>
+        <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9422,13 +9408,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9437,13 +9423,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9454,10 +9440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9477,21 +9463,21 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9515,13 +9501,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9539,7 +9525,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9554,13 +9540,13 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9571,10 +9557,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9585,7 +9571,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9597,16 +9583,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>441</v>
+        <v>356</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9632,13 +9618,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9656,13 +9642,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -9671,13 +9657,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9688,10 +9674,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9714,16 +9700,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>360</v>
+        <v>451</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9773,7 +9759,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9788,13 +9774,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9805,10 +9791,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9831,16 +9817,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9890,7 +9876,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9905,13 +9891,13 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9922,10 +9908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9936,7 +9922,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9948,17 +9934,15 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10007,13 +9991,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10022,13 +10006,13 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10039,10 +10023,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10065,13 +10049,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>467</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10122,7 +10106,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>466</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10134,16 +10118,16 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>471</v>
+        <v>172</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10154,10 +10138,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10168,7 +10152,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10180,13 +10164,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10225,31 +10209,29 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10258,7 +10240,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10269,12 +10251,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="B68" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10295,13 +10279,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>137</v>
+        <v>476</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10340,14 +10324,16 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC68" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>178</v>
@@ -10359,7 +10345,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10382,13 +10368,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10398,7 +10384,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10410,13 +10396,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10476,7 +10462,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10499,35 +10485,33 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C70" t="s" s="2">
         <v>485</v>
       </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>486</v>
+        <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>487</v>
@@ -10535,8 +10519,12 @@
       <c r="M70" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+      <c r="N70" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10584,7 +10572,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>178</v>
+        <v>489</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10593,7 +10581,7 @@
         <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>142</v>
@@ -10605,7 +10593,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10616,33 +10604,33 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>137</v>
+        <v>463</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>491</v>
@@ -10651,11 +10639,9 @@
         <v>492</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10703,19 +10689,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10724,7 +10710,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>134</v>
+        <v>494</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10735,10 +10721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10761,17 +10747,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>168</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>495</v>
+        <v>169</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10820,7 +10804,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>494</v>
+        <v>171</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10832,7 +10816,7 @@
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -10841,7 +10825,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>498</v>
+        <v>172</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10852,21 +10836,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10878,15 +10862,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10935,19 +10921,19 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10967,14 +10953,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>136</v>
+        <v>486</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10987,24 +10973,26 @@
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>138</v>
+        <v>487</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>175</v>
+        <v>488</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11052,7 +11040,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>178</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11073,7 +11061,7 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11084,46 +11072,44 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>137</v>
+        <v>499</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11171,19 +11157,19 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11192,7 +11178,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>134</v>
+        <v>503</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11203,10 +11189,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11229,16 +11215,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11288,7 +11274,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11309,7 +11295,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11320,10 +11306,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11346,7 +11332,7 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>510</v>
@@ -11355,7 +11341,7 @@
         <v>511</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11405,7 +11391,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11426,7 +11412,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11437,10 +11423,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11463,18 +11449,20 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>509</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11522,7 +11510,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11540,10 +11528,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11554,10 +11542,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11580,20 +11568,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>517</v>
+        <v>169</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11641,7 +11625,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>516</v>
+        <v>171</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11653,16 +11637,16 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>521</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>522</v>
+        <v>172</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11673,21 +11657,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11699,15 +11683,17 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11744,31 +11730,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11788,21 +11774,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11811,19 +11797,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>137</v>
+        <v>360</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>138</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>175</v>
+        <v>523</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>140</v>
+        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11861,31 +11847,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>178</v>
+        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11894,21 +11880,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>172</v>
+        <v>527</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11931,22 +11917,24 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
       </c>
@@ -11990,7 +11978,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11999,7 +11987,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -12011,21 +11999,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12045,72 +12033,70 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>364</v>
+        <v>538</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q83" t="s" s="2">
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="R83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
@@ -12118,7 +12104,7 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>103</v>
@@ -12127,24 +12113,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12167,16 +12153,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>542</v>
+        <v>499</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>545</v>
+        <v>502</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12226,7 +12212,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12244,24 +12230,24 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12284,16 +12270,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>506</v>
+        <v>554</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12343,7 +12329,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12361,24 +12347,24 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12401,17 +12387,15 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>509</v>
+        <v>168</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>556</v>
+        <v>169</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12460,7 +12444,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>555</v>
+        <v>171</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12472,16 +12456,16 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>560</v>
+        <v>172</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12492,21 +12476,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12518,15 +12502,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12563,31 +12549,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12607,21 +12593,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12630,21 +12616,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>137</v>
+        <v>560</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>138</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>175</v>
+        <v>562</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12680,31 +12668,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>178</v>
+        <v>565</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12713,21 +12701,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>172</v>
+        <v>566</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>82</v>
+        <v>567</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12744,30 +12732,30 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>564</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
       </c>
@@ -12787,13 +12775,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12811,7 +12799,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12832,21 +12820,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12863,32 +12851,30 @@
         <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>576</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>82</v>
+        <v>582</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12906,13 +12892,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -12930,7 +12916,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12951,21 +12937,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12988,24 +12974,24 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13047,7 +13033,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13056,7 +13042,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13068,21 +13054,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13105,24 +13091,26 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13164,7 +13152,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13173,7 +13161,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -13185,21 +13173,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13219,29 +13207,27 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>111</v>
+        <v>603</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
-        <v>603</v>
+        <v>82</v>
       </c>
       <c r="S93" t="s" s="2">
         <v>82</v>
@@ -13283,7 +13269,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13304,21 +13290,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13341,7 +13327,7 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>607</v>
+        <v>463</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>608</v>
@@ -13349,9 +13335,7 @@
       <c r="M94" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>360</v>
-      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13400,7 +13384,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13418,13 +13402,13 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13432,10 +13416,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13458,13 +13442,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>467</v>
+        <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>612</v>
+        <v>169</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>613</v>
+        <v>170</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13515,7 +13499,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>611</v>
+        <v>171</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13527,16 +13511,16 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>615</v>
+        <v>172</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13547,21 +13531,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13573,15 +13557,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13630,19 +13616,19 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13662,14 +13648,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>136</v>
+        <v>486</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13682,24 +13668,26 @@
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>138</v>
+        <v>487</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>175</v>
+        <v>488</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13747,7 +13735,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>178</v>
+        <v>489</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13768,7 +13756,7 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
@@ -13779,46 +13767,44 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>491</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>492</v>
+        <v>616</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13842,13 +13828,11 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13866,42 +13850,42 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>493</v>
+        <v>615</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>134</v>
+        <v>619</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13909,7 +13893,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>91</v>
@@ -13927,13 +13911,13 @@
         <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13959,11 +13943,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13981,10 +13967,10 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>91</v>
@@ -13999,24 +13985,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14039,16 +14025,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>192</v>
+        <v>631</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>628</v>
+        <v>356</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14074,31 +14060,31 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14113,38 +14099,38 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>633</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14156,16 +14142,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>360</v>
+        <v>641</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14215,13 +14201,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14230,13 +14216,13 @@
         <v>103</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14247,14 +14233,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14273,16 +14259,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14332,7 +14318,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14347,135 +14333,18 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -645,7 +645,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -739,7 +739,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -902,7 +902,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1140,7 +1140,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1286,7 +1286,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1409,7 +1409,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2003,7 +2003,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2026,7 +2026,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2045,7 +2045,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -1976,19 +1976,16 @@
     <t>MedicationRequest.substitution.reason</t>
   </si>
   <si>
-    <t>代替品を提供した（あるいは、しなかった）理由</t>
-  </si>
-  <si>
-    <t>代替品にしなければならなかった、あるいは代替品が認められなかった理由を示す。</t>
+    <t>後発医薬品への変更不可理由</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】後発医薬品への変更不可の理由を示す。令和6年保険改訂により、長期収載医薬品の変更不可を指定する場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
   </si>
   <si>
     <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
-    <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>
   </si>
   <si>
     <t>not mapped</t>
@@ -2392,7 +2389,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -13943,13 +13940,11 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Y99" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y99" s="2"/>
+      <c r="Z99" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13985,24 +13980,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AM99" t="s" s="2">
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>629</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14025,13 +14020,13 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>356</v>
@@ -14084,7 +14079,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14099,13 +14094,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14116,14 +14111,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14142,16 +14137,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14201,7 +14196,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14222,7 +14217,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14233,10 +14228,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14259,16 +14254,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14318,7 +14313,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14333,13 +14328,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3812" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -975,9 +975,6 @@
   </si>
   <si>
     <t>このMedicationRequestオーダの優先度。他のオーダと比較して表現される。</t>
-  </si>
-  <si>
-    <t>FHIRでは文字列の大きさが1MBを超えてはならない(SHALL NOT)。</t>
   </si>
   <si>
     <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
@@ -7371,9 +7368,7 @@
       <c r="M43" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="N43" t="s" s="2">
-        <v>306</v>
-      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7401,10 +7396,10 @@
         <v>185</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7437,16 +7432,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7454,10 +7449,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7480,16 +7475,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7539,7 +7534,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7560,7 +7555,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7571,10 +7566,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7597,13 +7592,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7654,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7675,7 +7670,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7686,10 +7681,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7712,16 +7707,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7771,7 +7766,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7786,27 +7781,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7829,16 +7824,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7888,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7903,27 +7898,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7946,16 +7941,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8005,7 +8000,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8020,27 +8015,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8063,16 +8058,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8122,7 +8117,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8137,16 +8132,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8154,10 +8149,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8180,13 +8175,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8237,7 +8232,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8252,27 +8247,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8295,16 +8290,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8354,7 +8349,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8369,16 +8364,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8386,10 +8381,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8412,16 +8407,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="N52" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8471,7 +8466,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8486,16 +8481,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8503,10 +8498,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8532,13 +8527,13 @@
         <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8568,7 +8563,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8586,7 +8581,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8601,13 +8596,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8618,10 +8613,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8644,16 +8639,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="N54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8703,7 +8698,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8724,10 +8719,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8735,10 +8730,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8764,13 +8759,13 @@
         <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8799,11 +8794,11 @@
         <v>282</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8820,7 +8815,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8835,27 +8830,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8878,16 +8873,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8937,7 +8932,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8952,16 +8947,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8969,10 +8964,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8995,16 +8990,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9054,7 +9049,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9069,13 +9064,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9086,10 +9081,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9115,13 +9110,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9171,7 +9166,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9192,7 +9187,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9203,10 +9198,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9229,16 +9224,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9288,7 +9283,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9303,13 +9298,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9320,10 +9315,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9349,14 +9344,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9405,7 +9400,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9420,13 +9415,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9437,10 +9432,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9466,13 +9461,13 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9501,11 +9496,11 @@
         <v>282</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9522,7 +9517,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9543,7 +9538,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9554,10 +9549,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9580,16 +9575,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9639,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9654,13 +9649,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9671,10 +9666,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9697,16 +9692,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9756,7 +9751,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9771,13 +9766,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9788,10 +9783,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9814,16 +9809,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9873,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9888,13 +9883,13 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9905,10 +9900,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9931,13 +9926,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9988,7 +9983,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10006,10 +10001,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10020,10 +10015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10049,10 +10044,10 @@
         <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10135,10 +10130,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10164,10 +10159,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10248,13 +10243,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10276,13 +10271,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10342,7 +10337,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10365,13 +10360,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10393,13 +10388,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10459,7 +10454,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10482,14 +10477,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10511,10 +10506,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10569,7 +10564,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10601,10 +10596,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10627,16 +10622,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10686,7 +10681,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10707,7 +10702,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10718,10 +10713,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10833,10 +10828,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10950,14 +10945,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10979,10 +10974,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11037,7 +11032,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11069,10 +11064,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11095,16 +11090,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11154,7 +11149,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11175,7 +11170,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11186,10 +11181,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11212,16 +11207,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>507</v>
-      </c>
       <c r="N76" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11271,7 +11266,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11292,7 +11287,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11303,10 +11298,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11329,16 +11324,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="N77" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11388,7 +11383,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11409,7 +11404,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11420,10 +11415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11449,16 +11444,16 @@
         <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11507,7 +11502,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11525,10 +11520,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11539,10 +11534,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11654,10 +11649,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11771,10 +11766,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11797,16 +11792,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11856,16 +11851,16 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI81" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11877,21 +11872,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11914,69 +11909,69 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="R82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11984,7 +11979,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11996,21 +11991,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12033,16 +12028,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12092,7 +12087,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12110,24 +12105,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AN83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>544</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12150,16 +12145,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="N84" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12209,7 +12204,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12227,24 +12222,24 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12267,16 +12262,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12326,7 +12321,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12344,10 +12339,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12358,10 +12353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12473,10 +12468,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12590,10 +12585,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12616,19 +12611,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12677,7 +12672,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12698,21 +12693,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>567</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12738,20 +12733,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q89" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q89" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12775,28 +12770,28 @@
         <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12817,21 +12812,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>577</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12857,63 +12852,63 @@
         <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12934,21 +12929,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>585</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12974,72 +12969,72 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI91" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13051,21 +13046,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13091,65 +13086,65 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13170,21 +13165,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13207,16 +13202,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13266,7 +13261,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13287,10 +13282,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13298,10 +13293,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13324,13 +13319,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13381,7 +13376,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13399,10 +13394,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13413,10 +13408,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13528,10 +13523,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13645,14 +13640,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13674,10 +13669,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13732,7 +13727,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13764,10 +13759,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13793,13 +13788,13 @@
         <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13829,7 +13824,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13847,7 +13842,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13865,24 +13860,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>620</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13908,13 +13903,13 @@
         <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13944,7 +13939,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -13962,7 +13957,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13980,24 +13975,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AM99" t="s" s="2">
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14020,16 +14015,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14079,7 +14074,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14094,13 +14089,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14111,14 +14106,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14137,16 +14132,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14196,7 +14191,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14217,7 +14212,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14228,10 +14223,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14254,16 +14249,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14313,7 +14308,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14328,13 +14323,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -1979,7 +1979,7 @@
     <t>【JP Core仕様】後発医薬品への変更不可の理由を示す。令和6年保険改訂により、長期収載医薬品の変更不可を指定する場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
   </si>
   <si>
-    <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
+    <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -1723,10 +1723,10 @@
     <t>許可されたリフィル回数</t>
   </si>
   <si>
-    <t>リフィル回数を示す整数である。患者が処方された薬を最初の払い出しから追加で受け取ることができる回数である。使用上の注意：この整数には最初の払い出しが含まれない。オーダが「30錠に加えて3回リフィル可」であれば、このオーダで合計で最大4回、120錠が患者に受け渡される。この数字を0とすることで，処方者がリフィルを許可しないということを明示することができる。</t>
-  </si>
-  <si>
-    <t>許可された払い出し回数は，最大でこの数字に1を足したものである。</t>
+    <t>リフィル回数を示す整数である。患者が処方された薬を最初の払い出しから追加で受け取ることができる回数である。使用上の注意：この整数には最初の払い出しが含まれない。オーダが「30錠に加えて3回リフィル可」であれば、このオーダで合計で最大4回、120錠が患者に受け渡される。この数字を0とすることで、処方者がリフィルを許可しないということを明示することができる。</t>
+  </si>
+  <si>
+    <t>許可された払い出し回数は、最大でこの数字に1を足したものである。</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -488,7 +488,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
@@ -1444,7 +1444,7 @@
     <t>他の属性では伝えることができなかったMedicationRequestについての付加的情報。</t>
   </si>
   <si>
-    <t>構造化されたアノテーションが内システムでは、作成者や記録時間のない一つのアノテーションで情報を伝達している。このエレメントに情報の修正を要する可能性があるためにナラティブな情報も必要としている。Annotationsには機械処理が可能で修正される（"modifying")情報を伝達することに使うべきではない(SHOULD NOT)。これがSHOULDである理由はユーザの行動を強制することはほぼ不可能であるからである。</t>
+    <t>構造化されたアノテーションが内システムでは、作成者や記録時間のない一つのアノテーションで情報を伝達している。このエレメントに情報の修正を要する可能性があるためにナラティブな情報も必要としている。Annotationsには機械処理が可能で修正される（"modifying")情報を伝達することに使うべきではない(SHOULD NOT)。これがSHOULDである理由はユーザーの行動を強制することはほぼ不可能であるからである。</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -2046,7 +2046,7 @@
     <t>ライフサイクルで関心のあるイベントのリスト</t>
   </si>
   <si>
-    <t>このリソースの現在のバージョンをユーザから見て関係していそうなキーとなる更新や状態遷移と識別される過去のバージョンのこのリソースあるいは調剤請求あるいはEvent ResourceについてのProvenance resourceへの参照。</t>
+    <t>このリソースの現在のバージョンをユーザーから見て関係していそうなキーとなる更新や状態遷移と識別される過去のバージョンのこのリソースあるいは調剤請求あるいはEvent ResourceについてのProvenance resourceへの参照。</t>
   </si>
   <si>
     <t>このエレメントには全てのバージョンのMedicationRequestについてのProvenanceが取り込まれているわけではない。「関連する」あるいは重要と思われたものだけである。現在のバージョンのResourceに関連したProvenance resourceを含めてはならない(SHALL NOT)。（もし、Provenanceとして「関連した」変化と思われれば、後の更新の一部として取り込まれる必要があるだろう。それまでは、このバージョンを_revincludeを使ってprovenanceとして指定して直接クエリーを発行することができる。全てのProvenanceがこのRequestについての履歴を対象として持つべきである。）</t>
